--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB7F1F0-86FE-47A4-95B2-174599E7AEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C511213D-20F8-4131-98FF-9CEF988A00D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="Cell" sheetId="4" r:id="rId3"/>
     <sheet name="Module" sheetId="5" r:id="rId4"/>
     <sheet name="PV Glass" sheetId="6" r:id="rId5"/>
-    <sheet name="info" sheetId="1" r:id="rId6"/>
+    <sheet name="fig" sheetId="7" r:id="rId6"/>
+    <sheet name="info" sheetId="1" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -198,7 +199,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -293,17 +294,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -321,6 +322,5804 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Polysilicon!$G$1:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> N-Type Recharge Polysilicon </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Polysilicon!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Polysilicon!$G$3:$G$12</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>39</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AB28-4013-B407-A432288B790C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Polysilicon!$J$1:$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> N-Type Dense Polysilicon (RMB) </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Polysilicon!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Polysilicon!$J$3:$J$12</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AB28-4013-B407-A432288B790C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Polysilicon!$M$1:$M$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> N-Type Granular Polysilicon (RMB) </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Polysilicon!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Polysilicon!$M$3:$M$12</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-AB28-4013-B407-A432288B790C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Polysilicon!$P$1:$P$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> Polysilicon Outside China (USD) </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Polysilicon!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Polysilicon!$P$3:$P$12</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.0_-;\-* #,##0.0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-AB28-4013-B407-A432288B790C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="961366127"/>
+        <c:axId val="961379087"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="961366127"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46387"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy\-mm;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="961379087"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="2"/>
+        <c:majorTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="961379087"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="961366127"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="700" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Wafer!$G$1:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> N-Type M10 Mono Wafer - 183mm/130μm (RMB) </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Wafer!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Wafer!$G$3:$G$12</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.05</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.05</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.98</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C55D-4858-98C1-05ABA56A643D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Wafer!$J$1:$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> N-Type G12 Mono Wafer - 210mm/130μm (RMB) </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Wafer!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Wafer!$J$3:$J$12</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.35</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C55D-4858-98C1-05ABA56A643D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Wafer!$M$1:$M$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> N-Type 210R Mono Wafer-210*182mm/130μm (RMB) </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Wafer!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Wafer!$M$3:$M$12</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.05</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C55D-4858-98C1-05ABA56A643D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1183437743"/>
+        <c:axId val="1183428623"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1183437743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46387"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy\-mm;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1183428623"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="2"/>
+        <c:majorTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1183428623"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0.60000000000000009"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1183437743"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Cell!$G$1:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>M10L TOPCon Cell (RMB)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Cell!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Cell!$G$3:$G$12</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.39</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.36</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8410-4F9F-B913-C45906D13F2C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Cell!$J$1:$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>G12 TOPCon Cell (RMB)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Cell!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Cell!$J$3:$J$12</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.39</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.36</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8410-4F9F-B913-C45906D13F2C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Cell!$M$1:$M$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>G12R TOPCon Cell (RMB)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Cell!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Cell!$M$3:$M$12</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.39</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.36</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8410-4F9F-B913-C45906D13F2C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1183551023"/>
+        <c:axId val="1183551503"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1183551023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46387"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy\-mm;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1183551503"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="2"/>
+        <c:majorTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1183551503"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1183551023"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="2.0000000000000004E-2"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Module!$G$1:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> 182mm TOPCon Module (RMB) </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Module!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Module!$G$3:$G$12</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.79</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4748-4EC9-A6AC-E57B807BE2B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Module!$J$1:$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> 210mm HJT Module (RMB) </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Module!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Module!$J$3:$J$12</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.76</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4748-4EC9-A6AC-E57B807BE2B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1183493423"/>
+        <c:axId val="1183484783"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1183493423"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46387"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy\-mm;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1183484783"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="2"/>
+        <c:majorTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1183484783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1183493423"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PV Glass'!$G$1:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> 2.0mm Double-glazed and Coated PV Glass (RMB) </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'PV Glass'!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'PV Glass'!$G$3:$G$12</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.0_-;\-* #,##0.0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-872C-451E-92FD-E5C9022CA320}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PV Glass'!$J$1:$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> 3.2mm Double-glazed and Coated PV Glass (RMB) </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'PV Glass'!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'PV Glass'!$J$3:$J$12</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.0_-;\-* #,##0.0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-872C-451E-92FD-E5C9022CA320}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PV Glass'!$M$1:$M$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> 2.0 Rear PV Glass (RMB) </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'PV Glass'!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'PV Glass'!$M$3:$M$12</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.0_-;\-* #,##0.0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-872C-451E-92FD-E5C9022CA320}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1183466543"/>
+        <c:axId val="1183500623"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1183466543"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46387"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy\-mm;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1183500623"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="2"/>
+        <c:majorTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1183500623"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="6"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1183466543"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B2A6A88-C94C-4C8D-AEAE-D9ECCC8452E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDD9D55E-7ADF-4E2E-92AE-891910ACEB98}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>185853</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>15486</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A013A410-3E2F-46FB-8A96-ADD97EB3B7DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>610885</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>16075</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>16076</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC3DC82E-AFED-400C-AF62-B49B352ED888}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>610885</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>602848</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>176835</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98891A78-D2DD-4E77-A0D9-D7BA43F20CD8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -586,11 +6385,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="14" width="9" style="12"/>
@@ -600,16 +6399,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="3" customFormat="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="16" t="s">
         <v>24</v>
       </c>
       <c r="E1" s="11" t="s">
@@ -650,10 +6449,10 @@
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="13"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="11" t="s">
         <v>26</v>
       </c>
@@ -697,10 +6496,10 @@
       <c r="U2" s="4"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="16">
+      <c r="A3" s="13">
         <v>46043</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="13">
         <v>46043</v>
       </c>
       <c r="C3" s="6">
@@ -752,10 +6551,10 @@
       <c r="U3" s="4"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="16">
+      <c r="A4" s="13">
         <v>46050</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="13">
         <v>46050</v>
       </c>
       <c r="C4" s="6">
@@ -807,10 +6606,10 @@
       <c r="U4" s="4"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="16">
+      <c r="A5" s="13">
         <v>46057</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="13">
         <v>46057</v>
       </c>
       <c r="C5" s="6">
@@ -857,10 +6656,10 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="16">
+      <c r="A6" s="13">
         <v>46064</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="13">
         <v>46064</v>
       </c>
       <c r="C6" s="6">
@@ -907,10 +6706,10 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="16">
+      <c r="A7" s="13">
         <v>46078</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="13">
         <v>46078</v>
       </c>
       <c r="C7" s="6">
@@ -957,10 +6756,10 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="16">
+      <c r="A8" s="13">
         <v>46085</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="13">
         <v>46085</v>
       </c>
       <c r="C8" s="6">
@@ -1007,10 +6806,10 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="16">
+      <c r="A9" s="13">
         <v>46092</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="13">
         <v>46092</v>
       </c>
       <c r="C9" s="6">
@@ -1057,10 +6856,10 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="16">
+      <c r="A10" s="13">
         <v>46099</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="13">
         <v>46099</v>
       </c>
       <c r="C10" s="6">
@@ -1107,10 +6906,10 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="16">
+      <c r="A11" s="13">
         <v>46106</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="13">
         <v>46106</v>
       </c>
       <c r="C11" s="6">
@@ -1153,6 +6952,56 @@
         <v>13.1</v>
       </c>
       <c r="P11" s="10">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" s="13">
+        <v>46113</v>
+      </c>
+      <c r="B12" s="13">
+        <v>46113</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="12">
+        <v>39</v>
+      </c>
+      <c r="F12" s="12">
+        <v>37</v>
+      </c>
+      <c r="G12" s="12">
+        <v>39</v>
+      </c>
+      <c r="H12" s="12">
+        <v>37</v>
+      </c>
+      <c r="I12" s="12">
+        <v>35</v>
+      </c>
+      <c r="J12" s="12">
+        <v>37</v>
+      </c>
+      <c r="K12" s="12">
+        <v>37</v>
+      </c>
+      <c r="L12" s="12">
+        <v>35</v>
+      </c>
+      <c r="M12" s="12">
+        <v>37</v>
+      </c>
+      <c r="N12" s="12">
+        <v>22</v>
+      </c>
+      <c r="O12" s="10">
+        <v>13.1</v>
+      </c>
+      <c r="P12" s="10">
         <v>17.5</v>
       </c>
     </row>
@@ -1171,11 +7020,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
@@ -1183,16 +7032,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="3" customFormat="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="16" t="s">
         <v>24</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -1227,10 +7076,10 @@
       <c r="P1" s="2"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="13"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="4" t="s">
         <v>26</v>
       </c>
@@ -1268,10 +7117,10 @@
       <c r="U2" s="4"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="16">
+      <c r="A3" s="13">
         <v>46043</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="13">
         <v>46043</v>
       </c>
       <c r="C3" s="6">
@@ -1317,10 +7166,10 @@
       <c r="U3" s="4"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="16">
+      <c r="A4" s="13">
         <v>46050</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="13">
         <v>46050</v>
       </c>
       <c r="C4" s="6">
@@ -1366,10 +7215,10 @@
       <c r="U4" s="4"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="16">
+      <c r="A5" s="13">
         <v>46057</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="13">
         <v>46057</v>
       </c>
       <c r="C5" s="6">
@@ -1407,10 +7256,10 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="16">
+      <c r="A6" s="13">
         <v>46064</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="13">
         <v>46064</v>
       </c>
       <c r="C6" s="6">
@@ -1448,10 +7297,10 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="16">
+      <c r="A7" s="13">
         <v>46078</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="13">
         <v>46078</v>
       </c>
       <c r="C7" s="6">
@@ -1489,10 +7338,10 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="16">
+      <c r="A8" s="13">
         <v>46085</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="13">
         <v>46085</v>
       </c>
       <c r="C8" s="6">
@@ -1530,10 +7379,10 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="16">
+      <c r="A9" s="13">
         <v>46092</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="13">
         <v>46092</v>
       </c>
       <c r="C9" s="6">
@@ -1571,10 +7420,10 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="16">
+      <c r="A10" s="13">
         <v>46099</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="13">
         <v>46099</v>
       </c>
       <c r="C10" s="6">
@@ -1612,10 +7461,10 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="16">
+      <c r="A11" s="13">
         <v>46106</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="13">
         <v>46106</v>
       </c>
       <c r="C11" s="6">
@@ -1650,6 +7499,47 @@
       </c>
       <c r="M11" s="8">
         <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" s="13">
+        <v>46113</v>
+      </c>
+      <c r="B12" s="13">
+        <v>46113</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.98</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0.98</v>
+      </c>
+      <c r="H12" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="I12" s="8">
+        <v>1.23</v>
+      </c>
+      <c r="J12" s="8">
+        <v>1.25</v>
+      </c>
+      <c r="K12" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="L12" s="8">
+        <v>1.02</v>
+      </c>
+      <c r="M12" s="8">
+        <v>1.05</v>
       </c>
     </row>
   </sheetData>
@@ -1666,11 +7556,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
@@ -1678,16 +7568,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="3" customFormat="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="16" t="s">
         <v>24</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -1722,10 +7612,10 @@
       <c r="P1" s="2"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="13"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="4" t="s">
         <v>26</v>
       </c>
@@ -1763,10 +7653,10 @@
       <c r="U2" s="4"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="16">
+      <c r="A3" s="13">
         <v>46043</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="13">
         <v>46043</v>
       </c>
       <c r="C3" s="6">
@@ -1812,10 +7702,10 @@
       <c r="U3" s="4"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="16">
+      <c r="A4" s="13">
         <v>46050</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="13">
         <v>46050</v>
       </c>
       <c r="C4" s="6">
@@ -1861,10 +7751,10 @@
       <c r="U4" s="4"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="16">
+      <c r="A5" s="13">
         <v>46057</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="13">
         <v>46057</v>
       </c>
       <c r="C5" s="6">
@@ -1902,10 +7792,10 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="16">
+      <c r="A6" s="13">
         <v>46064</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="13">
         <v>46064</v>
       </c>
       <c r="C6" s="6">
@@ -1943,10 +7833,10 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="16">
+      <c r="A7" s="13">
         <v>46078</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="13">
         <v>46078</v>
       </c>
       <c r="C7" s="6">
@@ -1984,10 +7874,10 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="16">
+      <c r="A8" s="13">
         <v>46085</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="13">
         <v>46085</v>
       </c>
       <c r="C8" s="6">
@@ -2025,10 +7915,10 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="16">
+      <c r="A9" s="13">
         <v>46092</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="13">
         <v>46092</v>
       </c>
       <c r="C9" s="6">
@@ -2066,10 +7956,10 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="16">
+      <c r="A10" s="13">
         <v>46099</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="13">
         <v>46099</v>
       </c>
       <c r="C10" s="6">
@@ -2107,10 +7997,10 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="16">
+      <c r="A11" s="13">
         <v>46106</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="13">
         <v>46106</v>
       </c>
       <c r="C11" s="6">
@@ -2145,6 +8035,47 @@
       </c>
       <c r="M11" s="8">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" s="13">
+        <v>46113</v>
+      </c>
+      <c r="B12" s="13">
+        <v>46113</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.37</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0.35</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0.36</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0.37</v>
+      </c>
+      <c r="I12" s="8">
+        <v>0.35</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0.36</v>
+      </c>
+      <c r="K12" s="8">
+        <v>0.37</v>
+      </c>
+      <c r="L12" s="8">
+        <v>0.35</v>
+      </c>
+      <c r="M12" s="8">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -2161,11 +8092,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
@@ -2173,16 +8104,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="3" customFormat="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="16" t="s">
         <v>24</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -2211,10 +8142,10 @@
       <c r="P1" s="2"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="13"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="4" t="s">
         <v>26</v>
       </c>
@@ -2246,10 +8177,10 @@
       <c r="U2" s="4"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="16">
+      <c r="A3" s="13">
         <v>46043</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="13">
         <v>46043</v>
       </c>
       <c r="C3" s="6">
@@ -2289,10 +8220,10 @@
       <c r="U3" s="4"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="16">
+      <c r="A4" s="13">
         <v>46050</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="13">
         <v>46050</v>
       </c>
       <c r="C4" s="6">
@@ -2332,10 +8263,10 @@
       <c r="U4" s="4"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="16">
+      <c r="A5" s="13">
         <v>46057</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="13">
         <v>46057</v>
       </c>
       <c r="C5" s="6">
@@ -2364,10 +8295,10 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="16">
+      <c r="A6" s="13">
         <v>46064</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="13">
         <v>46064</v>
       </c>
       <c r="C6" s="6">
@@ -2396,10 +8327,10 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="16">
+      <c r="A7" s="13">
         <v>46078</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="13">
         <v>46078</v>
       </c>
       <c r="C7" s="6">
@@ -2428,10 +8359,10 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="16">
+      <c r="A8" s="13">
         <v>46085</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="13">
         <v>46085</v>
       </c>
       <c r="C8" s="6">
@@ -2460,10 +8391,10 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="16">
+      <c r="A9" s="13">
         <v>46092</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="13">
         <v>46092</v>
       </c>
       <c r="C9" s="6">
@@ -2492,10 +8423,10 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="16">
+      <c r="A10" s="13">
         <v>46099</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="13">
         <v>46099</v>
       </c>
       <c r="C10" s="6">
@@ -2524,10 +8455,10 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="16">
+      <c r="A11" s="13">
         <v>46106</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="13">
         <v>46106</v>
       </c>
       <c r="C11" s="6">
@@ -2552,6 +8483,38 @@
         <v>0.7</v>
       </c>
       <c r="J11" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" s="13">
+        <v>46113</v>
+      </c>
+      <c r="B12" s="13">
+        <v>46113</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.85</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0.78</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0.79</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="I12" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="J12" s="8">
         <v>0.76</v>
       </c>
     </row>
@@ -2569,11 +8532,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
@@ -2587,16 +8550,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="3" customFormat="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="16" t="s">
         <v>24</v>
       </c>
       <c r="E1" s="11" t="s">
@@ -2631,10 +8594,10 @@
       <c r="P1" s="2"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="13"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="11" t="s">
         <v>26</v>
       </c>
@@ -2672,10 +8635,10 @@
       <c r="U2" s="4"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="16">
+      <c r="A3" s="13">
         <v>46043</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="13">
         <v>46043</v>
       </c>
       <c r="C3" s="6">
@@ -2721,10 +8684,10 @@
       <c r="U3" s="4"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="16">
+      <c r="A4" s="13">
         <v>46050</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="13">
         <v>46050</v>
       </c>
       <c r="C4" s="6">
@@ -2770,10 +8733,10 @@
       <c r="U4" s="4"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="16">
+      <c r="A5" s="13">
         <v>46057</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="13">
         <v>46057</v>
       </c>
       <c r="C5" s="6">
@@ -2811,10 +8774,10 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="16">
+      <c r="A6" s="13">
         <v>46064</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="13">
         <v>46064</v>
       </c>
       <c r="C6" s="6">
@@ -2852,10 +8815,10 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="16">
+      <c r="A7" s="13">
         <v>46078</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="13">
         <v>46078</v>
       </c>
       <c r="C7" s="6">
@@ -2893,10 +8856,10 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="16">
+      <c r="A8" s="13">
         <v>46085</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="13">
         <v>46085</v>
       </c>
       <c r="C8" s="6">
@@ -2934,10 +8897,10 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="16">
+      <c r="A9" s="13">
         <v>46092</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="13">
         <v>46092</v>
       </c>
       <c r="C9" s="6">
@@ -2975,10 +8938,10 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="16">
+      <c r="A10" s="13">
         <v>46099</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="13">
         <v>46099</v>
       </c>
       <c r="C10" s="6">
@@ -3016,10 +8979,10 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="16">
+      <c r="A11" s="13">
         <v>46106</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="13">
         <v>46106</v>
       </c>
       <c r="C11" s="6">
@@ -3053,6 +9016,47 @@
         <v>9</v>
       </c>
       <c r="M11" s="10">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" s="13">
+        <v>46113</v>
+      </c>
+      <c r="B12" s="13">
+        <v>46113</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="12">
+        <v>12</v>
+      </c>
+      <c r="F12" s="12">
+        <v>11</v>
+      </c>
+      <c r="G12" s="10">
+        <v>11.5</v>
+      </c>
+      <c r="H12" s="12">
+        <v>19</v>
+      </c>
+      <c r="I12" s="12">
+        <v>18</v>
+      </c>
+      <c r="J12" s="10">
+        <v>18.5</v>
+      </c>
+      <c r="K12" s="12">
+        <v>10</v>
+      </c>
+      <c r="L12" s="12">
+        <v>9</v>
+      </c>
+      <c r="M12" s="10">
         <v>9.5</v>
       </c>
     </row>
@@ -3069,6 +9073,16 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9750F8-1F5B-4526-B393-530CBB79CB33}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.5"/>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CAD09A-E112-49E2-BE2A-18D37F91815C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632FA435-0217-4FE1-8C3F-56B6D98A69C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -26,15 +26,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -198,24 +195,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -228,7 +225,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -265,7 +262,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -278,32 +275,32 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -311,8 +308,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,7 +327,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -419,7 +416,7 @@
             <c:numRef>
               <c:f>Polysilicon!$G$3:$G$12</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>53</c:v>
@@ -533,7 +530,7 @@
             <c:numRef>
               <c:f>Polysilicon!$J$3:$J$12</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>52</c:v>
@@ -647,7 +644,7 @@
             <c:numRef>
               <c:f>Polysilicon!$M$3:$M$12</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>50</c:v>
@@ -889,7 +886,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -965,6 +962,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -972,7 +970,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1008,7 +1005,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1530,6 +1527,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1537,7 +1535,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1573,7 +1570,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2095,6 +2092,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2102,7 +2100,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2138,7 +2135,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2545,6 +2542,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2552,7 +2550,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2588,7 +2585,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3110,6 +3107,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3117,7 +3115,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6388,20 +6385,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="14" width="9" style="12"/>
     <col min="15" max="16" width="9" style="10"/>
     <col min="17" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -6451,7 +6448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -6498,7 +6495,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -6553,7 +6550,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -6608,7 +6605,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -6658,7 +6655,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -6708,7 +6705,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -6758,7 +6755,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -6808,7 +6805,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -6858,7 +6855,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -6908,7 +6905,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -6958,7 +6955,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -7005,6 +7002,56 @@
         <v>13.1</v>
       </c>
       <c r="P12" s="10">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" s="13">
+        <v>46120</v>
+      </c>
+      <c r="B13" s="13">
+        <v>46120</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="12">
+        <v>39</v>
+      </c>
+      <c r="F13" s="12">
+        <v>37</v>
+      </c>
+      <c r="G13" s="12">
+        <v>39</v>
+      </c>
+      <c r="H13" s="12">
+        <v>37</v>
+      </c>
+      <c r="I13" s="12">
+        <v>35</v>
+      </c>
+      <c r="J13" s="12">
+        <v>37</v>
+      </c>
+      <c r="K13" s="12">
+        <v>37</v>
+      </c>
+      <c r="L13" s="12">
+        <v>35</v>
+      </c>
+      <c r="M13" s="12">
+        <v>37</v>
+      </c>
+      <c r="N13" s="12">
+        <v>22</v>
+      </c>
+      <c r="O13" s="10">
+        <v>13.1</v>
+      </c>
+      <c r="P13" s="10">
         <v>17.5</v>
       </c>
     </row>
@@ -7023,18 +7070,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -7078,7 +7125,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -7119,7 +7166,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -7168,7 +7215,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -7217,7 +7264,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -7258,7 +7305,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -7299,7 +7346,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -7340,7 +7387,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -7381,7 +7428,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -7422,7 +7469,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -7463,7 +7510,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -7504,7 +7551,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -7543,6 +7590,47 @@
       </c>
       <c r="M12" s="8">
         <v>1.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" s="13">
+        <v>46120</v>
+      </c>
+      <c r="B13" s="13">
+        <v>46120</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0.93</v>
+      </c>
+      <c r="H13" s="8">
+        <v>1.25</v>
+      </c>
+      <c r="I13" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="J13" s="8">
+        <v>1.23</v>
+      </c>
+      <c r="K13" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="L13" s="8">
+        <v>1</v>
+      </c>
+      <c r="M13" s="8">
+        <v>1.03</v>
       </c>
     </row>
   </sheetData>
@@ -7559,18 +7647,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -7614,7 +7702,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -7655,7 +7743,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -7704,7 +7792,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -7753,7 +7841,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -7794,7 +7882,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -7835,7 +7923,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -7876,7 +7964,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -7917,7 +8005,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -7958,7 +8046,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -7999,7 +8087,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -8040,7 +8128,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -8078,6 +8166,47 @@
         <v>0.35</v>
       </c>
       <c r="M12" s="8">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" s="13">
+        <v>46120</v>
+      </c>
+      <c r="B13" s="13">
+        <v>46120</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.36</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0.36</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0.36</v>
+      </c>
+      <c r="L13" s="8">
+        <v>0.35</v>
+      </c>
+      <c r="M13" s="8">
         <v>0.36</v>
       </c>
     </row>
@@ -8095,18 +8224,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -8144,7 +8273,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -8179,7 +8308,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -8222,7 +8351,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -8265,7 +8394,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -8297,7 +8426,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -8329,7 +8458,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -8361,7 +8490,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -8393,7 +8522,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -8425,7 +8554,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -8457,7 +8586,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -8489,7 +8618,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -8518,6 +8647,38 @@
         <v>0.7</v>
       </c>
       <c r="J12" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" s="13">
+        <v>46120</v>
+      </c>
+      <c r="B13" s="13">
+        <v>46120</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.85</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0.78</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0.79</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="J13" s="8">
         <v>0.76</v>
       </c>
     </row>
@@ -8535,13 +8696,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
     <col min="7" max="7" width="9" style="10"/>
     <col min="8" max="9" width="9" style="12"/>
@@ -8552,7 +8713,7 @@
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -8596,7 +8757,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -8637,7 +8798,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -8686,7 +8847,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -8735,7 +8896,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -8776,7 +8937,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -8817,7 +8978,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -8858,7 +9019,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -8899,7 +9060,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -8940,7 +9101,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -8981,7 +9142,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -9022,7 +9183,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -9061,6 +9222,47 @@
       </c>
       <c r="M12" s="10">
         <v>9.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" s="13">
+        <v>46120</v>
+      </c>
+      <c r="B13" s="13">
+        <v>46120</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="12">
+        <v>11.5</v>
+      </c>
+      <c r="F13" s="12">
+        <v>10.5</v>
+      </c>
+      <c r="G13" s="10">
+        <v>11</v>
+      </c>
+      <c r="H13" s="12">
+        <v>18.5</v>
+      </c>
+      <c r="I13" s="12">
+        <v>17.5</v>
+      </c>
+      <c r="J13" s="10">
+        <v>18</v>
+      </c>
+      <c r="K13" s="12">
+        <v>9.5</v>
+      </c>
+      <c r="L13" s="12">
+        <v>8.5</v>
+      </c>
+      <c r="M13" s="10">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -9078,7 +9280,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9750F8-1F5B-4526-B393-530CBB79CB33}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9090,18 +9292,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9109,25 +9311,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -9135,19 +9337,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -9155,19 +9357,19 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -9175,13 +9377,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -9189,13 +9391,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>20</v>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632FA435-0217-4FE1-8C3F-56B6D98A69C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9BE817-E930-4078-85DA-6427DB66403A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -25,6 +25,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -195,24 +198,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -225,7 +228,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -262,7 +265,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -275,32 +278,32 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -308,8 +311,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -327,7 +330,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -375,10 +378,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Polysilicon!$B$3:$B$12</c:f>
+              <c:f>Polysilicon!$B$3:$B$1112</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>46043</c:v>
                 </c:pt>
@@ -408,16 +411,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Polysilicon!$G$3:$G$12</c:f>
+              <c:f>Polysilicon!$G$3:$G$1112</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>53</c:v>
                 </c:pt>
@@ -446,6 +452,9 @@
                   <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>39</c:v>
                 </c:pt>
               </c:numCache>
@@ -489,10 +498,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Polysilicon!$B$3:$B$12</c:f>
+              <c:f>Polysilicon!$B$3:$B$1112</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>46043</c:v>
                 </c:pt>
@@ -522,16 +531,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Polysilicon!$J$3:$J$12</c:f>
+              <c:f>Polysilicon!$J$3:$J$1112</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>52</c:v>
                 </c:pt>
@@ -560,6 +572,9 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -603,10 +618,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Polysilicon!$B$3:$B$12</c:f>
+              <c:f>Polysilicon!$B$3:$B$1112</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>46043</c:v>
                 </c:pt>
@@ -636,16 +651,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Polysilicon!$M$3:$M$12</c:f>
+              <c:f>Polysilicon!$M$3:$M$1112</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>50</c:v>
                 </c:pt>
@@ -674,6 +692,9 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -717,10 +738,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Polysilicon!$B$3:$B$12</c:f>
+              <c:f>Polysilicon!$B$3:$B$1112</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>46043</c:v>
                 </c:pt>
@@ -750,16 +771,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Polysilicon!$P$3:$P$12</c:f>
+              <c:f>Polysilicon!$P$3:$P$1112</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.0_-;\-* #,##0.0_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>17.5</c:v>
                 </c:pt>
@@ -788,6 +812,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -886,7 +913,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -962,7 +989,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -970,6 +996,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1005,7 +1032,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1053,10 +1080,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Wafer!$B$3:$B$12</c:f>
+              <c:f>Wafer!$B$3:$B$1112</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>46043</c:v>
                 </c:pt>
@@ -1086,16 +1113,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Wafer!$G$3:$G$12</c:f>
+              <c:f>Wafer!$G$3:$G$1112</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>1.3</c:v>
                 </c:pt>
@@ -1125,6 +1155,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.93</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1167,10 +1200,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Wafer!$B$3:$B$12</c:f>
+              <c:f>Wafer!$B$3:$B$1112</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>46043</c:v>
                 </c:pt>
@@ -1200,16 +1233,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Wafer!$J$3:$J$12</c:f>
+              <c:f>Wafer!$J$3:$J$1112</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>1.6</c:v>
                 </c:pt>
@@ -1239,6 +1275,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.23</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1281,10 +1320,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Wafer!$B$3:$B$12</c:f>
+              <c:f>Wafer!$B$3:$B$1112</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>46043</c:v>
                 </c:pt>
@@ -1314,16 +1353,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Wafer!$M$3:$M$12</c:f>
+              <c:f>Wafer!$M$3:$M$1112</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>1.4</c:v>
                 </c:pt>
@@ -1353,6 +1395,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>1.05</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.03</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1527,7 +1572,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1535,6 +1579,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1570,7 +1615,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1618,10 +1663,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Cell!$B$3:$B$12</c:f>
+              <c:f>Cell!$B$3:$B$1112</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>46043</c:v>
                 </c:pt>
@@ -1651,6 +1696,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1732,10 +1780,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Cell!$B$3:$B$12</c:f>
+              <c:f>Cell!$B$3:$B$1112</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>46043</c:v>
                 </c:pt>
@@ -1765,6 +1813,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1846,10 +1897,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Cell!$B$3:$B$12</c:f>
+              <c:f>Cell!$B$3:$B$1112</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>46043</c:v>
                 </c:pt>
@@ -1879,16 +1930,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cell!$M$3:$M$12</c:f>
+              <c:f>Cell!$M$3:$M$1112</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>0.41</c:v>
                 </c:pt>
@@ -1917,6 +1971,9 @@
                   <c:v>0.39</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.36</c:v>
                 </c:pt>
               </c:numCache>
@@ -2092,7 +2149,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2100,6 +2156,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2135,7 +2192,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2183,10 +2240,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$3:$B$12</c:f>
+              <c:f>Module!$B$3:$B$1112</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>46043</c:v>
                 </c:pt>
@@ -2216,16 +2273,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$G$3:$G$12</c:f>
+              <c:f>Module!$G$3:$G$1112</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>0.79</c:v>
                 </c:pt>
@@ -2254,6 +2314,9 @@
                   <c:v>0.79</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.79</c:v>
                 </c:pt>
               </c:numCache>
@@ -2297,10 +2360,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$3:$B$12</c:f>
+              <c:f>Module!$B$3:$B$1112</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>46043</c:v>
                 </c:pt>
@@ -2330,16 +2393,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$J$3:$J$12</c:f>
+              <c:f>Module!$J$3:$J$1112</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>0.72</c:v>
                 </c:pt>
@@ -2368,6 +2434,9 @@
                   <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -2542,7 +2611,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2550,6 +2618,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2585,7 +2654,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2633,10 +2702,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'PV Glass'!$B$3:$B$12</c:f>
+              <c:f>'PV Glass'!$B$3:$B$1112</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>46043</c:v>
                 </c:pt>
@@ -2666,16 +2735,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'PV Glass'!$G$3:$G$12</c:f>
+              <c:f>'PV Glass'!$G$3:$G$1112</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.0_-;\-* #,##0.0_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>11.5</c:v>
                 </c:pt>
@@ -2705,6 +2777,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2747,10 +2822,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'PV Glass'!$B$3:$B$12</c:f>
+              <c:f>'PV Glass'!$B$3:$B$1112</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>46043</c:v>
                 </c:pt>
@@ -2780,16 +2855,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'PV Glass'!$J$3:$J$12</c:f>
+              <c:f>'PV Glass'!$J$3:$J$1112</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.0_-;\-* #,##0.0_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>18.5</c:v>
                 </c:pt>
@@ -2819,6 +2897,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2861,10 +2942,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'PV Glass'!$B$3:$B$12</c:f>
+              <c:f>'PV Glass'!$B$3:$B$1112</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>46043</c:v>
                 </c:pt>
@@ -2894,16 +2975,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'PV Glass'!$M$3:$M$12</c:f>
+              <c:f>'PV Glass'!$M$3:$M$1112</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.0_-;\-* #,##0.0_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>9.5</c:v>
                 </c:pt>
@@ -2933,6 +3017,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3107,7 +3194,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3115,6 +3201,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6386,19 +6473,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
   <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="14" width="9" style="12"/>
     <col min="15" max="16" width="9" style="10"/>
     <col min="17" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1">
+    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -6448,7 +6535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -6495,7 +6582,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -6550,7 +6637,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -6605,7 +6692,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -6655,7 +6742,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -6705,7 +6792,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -6755,7 +6842,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -6805,7 +6892,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -6855,7 +6942,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -6905,7 +6992,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -6955,7 +7042,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -7005,7 +7092,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="13">
         <v>46120</v>
       </c>
@@ -7071,17 +7158,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
   <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1">
+    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -7125,7 +7212,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -7166,7 +7253,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -7215,7 +7302,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -7264,7 +7351,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -7305,7 +7392,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -7346,7 +7433,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -7387,7 +7474,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -7428,7 +7515,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -7469,7 +7556,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -7510,7 +7597,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -7551,7 +7638,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -7592,7 +7679,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="13">
         <v>46120</v>
       </c>
@@ -7648,17 +7735,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
   <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1">
+    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -7702,7 +7789,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -7743,7 +7830,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -7792,7 +7879,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -7841,7 +7928,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -7882,7 +7969,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -7923,7 +8010,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -7964,7 +8051,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -8005,7 +8092,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -8046,7 +8133,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -8087,7 +8174,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -8128,7 +8215,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -8169,7 +8256,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="13">
         <v>46120</v>
       </c>
@@ -8225,17 +8312,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
   <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1">
+    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -8273,7 +8360,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -8308,7 +8395,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -8351,7 +8438,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -8394,7 +8481,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -8426,7 +8513,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -8458,7 +8545,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -8490,7 +8577,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -8522,7 +8609,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -8554,7 +8641,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -8586,7 +8673,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -8618,7 +8705,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -8650,7 +8737,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="13">
         <v>46120</v>
       </c>
@@ -8697,12 +8784,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
   <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
     <col min="7" max="7" width="9" style="10"/>
     <col min="8" max="9" width="9" style="12"/>
@@ -8713,7 +8800,7 @@
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1">
+    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -8757,7 +8844,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -8798,7 +8885,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>46043</v>
       </c>
@@ -8847,7 +8934,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>46050</v>
       </c>
@@ -8896,7 +8983,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>46057</v>
       </c>
@@ -8937,7 +9024,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>46064</v>
       </c>
@@ -8978,7 +9065,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>46078</v>
       </c>
@@ -9019,7 +9106,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
         <v>46085</v>
       </c>
@@ -9060,7 +9147,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
         <v>46092</v>
       </c>
@@ -9101,7 +9188,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
         <v>46099</v>
       </c>
@@ -9142,7 +9229,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <v>46106</v>
       </c>
@@ -9183,7 +9270,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
         <v>46113</v>
       </c>
@@ -9224,7 +9311,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="13">
         <v>46120</v>
       </c>
@@ -9280,7 +9367,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9750F8-1F5B-4526-B393-530CBB79CB33}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9292,18 +9379,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9311,25 +9398,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -9337,19 +9424,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -9357,19 +9444,19 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -9377,13 +9464,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -9391,13 +9478,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>20</v>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9BE817-E930-4078-85DA-6427DB66403A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86974DEC-33C8-4FDB-9E42-46EFB1AFCC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -26,15 +26,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -415,6 +412,9 @@
                 <c:pt idx="10">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -456,6 +456,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -535,6 +538,9 @@
                 <c:pt idx="10">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -576,6 +582,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -655,6 +664,9 @@
                 <c:pt idx="10">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -696,6 +708,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -775,6 +790,9 @@
                 <c:pt idx="10">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -815,6 +833,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -989,6 +1010,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -996,7 +1018,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1117,6 +1138,9 @@
                 <c:pt idx="10">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1158,6 +1182,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1237,6 +1264,9 @@
                 <c:pt idx="10">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1277,6 +1307,9 @@
                   <c:v>1.25</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>1.23</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>1.23</c:v>
                 </c:pt>
               </c:numCache>
@@ -1357,6 +1390,9 @@
                 <c:pt idx="10">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1397,6 +1433,9 @@
                   <c:v>1.05</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>1.03</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>1.03</c:v>
                 </c:pt>
               </c:numCache>
@@ -1572,6 +1611,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1579,7 +1619,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1700,6 +1739,9 @@
                 <c:pt idx="10">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1817,6 +1859,9 @@
                 <c:pt idx="10">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1934,6 +1979,9 @@
                 <c:pt idx="10">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1975,6 +2023,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.34</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2055,6 +2106,7 @@
         <c:axId val="1183551503"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0.30000000000000004"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2149,6 +2201,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2156,7 +2209,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2277,6 +2329,9 @@
                 <c:pt idx="10">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2317,6 +2372,9 @@
                   <c:v>0.79</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>0.79</c:v>
                 </c:pt>
               </c:numCache>
@@ -2397,6 +2455,9 @@
                 <c:pt idx="10">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2437,6 +2498,9 @@
                   <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>0.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -2611,6 +2675,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2618,7 +2683,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2739,6 +2803,9 @@
                 <c:pt idx="10">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2780,6 +2847,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2859,6 +2929,9 @@
                 <c:pt idx="10">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2900,6 +2973,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>17.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2979,6 +3055,9 @@
                 <c:pt idx="10">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3020,6 +3099,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3194,6 +3276,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3201,7 +3284,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6472,13 +6554,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="14" width="9" style="12"/>
     <col min="15" max="16" width="9" style="10"/>
     <col min="17" max="21" width="9" style="8"/>
@@ -7139,6 +7221,56 @@
         <v>13.1</v>
       </c>
       <c r="P13" s="10">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A14" s="13">
+        <v>46127</v>
+      </c>
+      <c r="B14" s="13">
+        <v>46127</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="12">
+        <v>39</v>
+      </c>
+      <c r="F14" s="12">
+        <v>35</v>
+      </c>
+      <c r="G14" s="12">
+        <v>37</v>
+      </c>
+      <c r="H14" s="12">
+        <v>37</v>
+      </c>
+      <c r="I14" s="12">
+        <v>33</v>
+      </c>
+      <c r="J14" s="12">
+        <v>35</v>
+      </c>
+      <c r="K14" s="12">
+        <v>36</v>
+      </c>
+      <c r="L14" s="12">
+        <v>32</v>
+      </c>
+      <c r="M14" s="12">
+        <v>34</v>
+      </c>
+      <c r="N14" s="12">
+        <v>22</v>
+      </c>
+      <c r="O14" s="10">
+        <v>13.1</v>
+      </c>
+      <c r="P14" s="10">
         <v>17.5</v>
       </c>
     </row>
@@ -7157,13 +7289,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
@@ -7717,6 +7849,47 @@
         <v>1</v>
       </c>
       <c r="M13" s="8">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A14" s="13">
+        <v>46127</v>
+      </c>
+      <c r="B14" s="13">
+        <v>46127</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0.92</v>
+      </c>
+      <c r="H14" s="8">
+        <v>1.25</v>
+      </c>
+      <c r="I14" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="J14" s="8">
+        <v>1.23</v>
+      </c>
+      <c r="K14" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="L14" s="8">
+        <v>1</v>
+      </c>
+      <c r="M14" s="8">
         <v>1.03</v>
       </c>
     </row>
@@ -7734,13 +7907,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
@@ -8295,6 +8468,47 @@
       </c>
       <c r="M13" s="8">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A14" s="13">
+        <v>46127</v>
+      </c>
+      <c r="B14" s="13">
+        <v>46127</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="I14" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="K14" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="L14" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -8311,13 +8525,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="8"/>
     <col min="22" max="16384" width="9" style="5"/>
   </cols>
@@ -8769,6 +8983,38 @@
         <v>0.76</v>
       </c>
     </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A14" s="13">
+        <v>46127</v>
+      </c>
+      <c r="B14" s="13">
+        <v>46127</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.85</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0.78</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0.79</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="I14" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -8783,13 +9029,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
     <col min="7" max="7" width="9" style="10"/>
     <col min="8" max="9" width="9" style="12"/>
@@ -9350,6 +9596,47 @@
       </c>
       <c r="M13" s="10">
         <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A14" s="13">
+        <v>46127</v>
+      </c>
+      <c r="B14" s="13">
+        <v>46127</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="12">
+        <v>11</v>
+      </c>
+      <c r="F14" s="12">
+        <v>10</v>
+      </c>
+      <c r="G14" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="H14" s="12">
+        <v>18.5</v>
+      </c>
+      <c r="I14" s="12">
+        <v>17</v>
+      </c>
+      <c r="J14" s="10">
+        <v>17.75</v>
+      </c>
+      <c r="K14" s="12">
+        <v>9</v>
+      </c>
+      <c r="L14" s="12">
+        <v>8.5</v>
+      </c>
+      <c r="M14" s="10">
+        <v>8.75</v>
       </c>
     </row>
   </sheetData>
@@ -9367,7 +9654,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9750F8-1F5B-4526-B393-530CBB79CB33}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9379,18 +9666,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9398,25 +9685,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -9424,19 +9711,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -9444,19 +9731,19 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -9464,13 +9751,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -9478,13 +9765,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>20</v>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDE9178-3DA1-4F7F-AA84-2189E2CC630A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FABBDA9-CAEA-46E4-85DF-E4F13DF600D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -418,6 +418,9 @@
                 <c:pt idx="12">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -464,6 +467,9 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -550,6 +556,9 @@
                 <c:pt idx="12">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -596,6 +605,9 @@
                   <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>35</c:v>
                 </c:pt>
               </c:numCache>
@@ -682,6 +694,9 @@
                 <c:pt idx="12">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -728,6 +743,9 @@
                   <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
@@ -814,6 +832,9 @@
                 <c:pt idx="12">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -860,6 +881,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1168,6 +1192,9 @@
                 <c:pt idx="12">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1214,6 +1241,9 @@
                   <c:v>0.92</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>0.92</c:v>
                 </c:pt>
               </c:numCache>
@@ -1300,6 +1330,9 @@
                 <c:pt idx="12">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1346,6 +1379,9 @@
                   <c:v>1.23</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>1.23</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>1.23</c:v>
                 </c:pt>
               </c:numCache>
@@ -1432,6 +1468,9 @@
                 <c:pt idx="12">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1478,6 +1517,9 @@
                   <c:v>1.03</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>1.03</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>1.03</c:v>
                 </c:pt>
               </c:numCache>
@@ -1787,6 +1829,9 @@
                 <c:pt idx="12">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1910,6 +1955,9 @@
                 <c:pt idx="12">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2033,6 +2081,9 @@
                 <c:pt idx="12">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2080,6 +2131,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.33500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.33</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2389,6 +2443,9 @@
                 <c:pt idx="12">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2436,6 +2493,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.78</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2521,6 +2581,9 @@
                 <c:pt idx="12">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2567,6 +2630,9 @@
                   <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>0.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -2875,6 +2941,9 @@
                 <c:pt idx="12">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2921,6 +2990,9 @@
                   <c:v>10.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>10.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3007,6 +3079,9 @@
                 <c:pt idx="12">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3053,6 +3128,9 @@
                   <c:v>17.75</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>17.75</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>17.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -3139,6 +3217,9 @@
                 <c:pt idx="12">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3185,6 +3266,9 @@
                   <c:v>8.75</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>8.75</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>8.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -6638,7 +6722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
@@ -7405,6 +7489,56 @@
         <v>13.1</v>
       </c>
       <c r="P15" s="10">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A16" s="13">
+        <v>46141</v>
+      </c>
+      <c r="B16" s="13">
+        <v>46141</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="12">
+        <v>39</v>
+      </c>
+      <c r="F16" s="12">
+        <v>35</v>
+      </c>
+      <c r="G16" s="12">
+        <v>37</v>
+      </c>
+      <c r="H16" s="12">
+        <v>37</v>
+      </c>
+      <c r="I16" s="12">
+        <v>33</v>
+      </c>
+      <c r="J16" s="12">
+        <v>35</v>
+      </c>
+      <c r="K16" s="12">
+        <v>36</v>
+      </c>
+      <c r="L16" s="12">
+        <v>32</v>
+      </c>
+      <c r="M16" s="12">
+        <v>34</v>
+      </c>
+      <c r="N16" s="12">
+        <v>22</v>
+      </c>
+      <c r="O16" s="10">
+        <v>13.1</v>
+      </c>
+      <c r="P16" s="10">
         <v>17.5</v>
       </c>
     </row>
@@ -7423,7 +7557,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
@@ -8065,6 +8199,47 @@
         <v>1</v>
       </c>
       <c r="M15" s="8">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A16" s="13">
+        <v>46141</v>
+      </c>
+      <c r="B16" s="13">
+        <v>46141</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="G16" s="8">
+        <v>0.92</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1.25</v>
+      </c>
+      <c r="I16" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="J16" s="8">
+        <v>1.23</v>
+      </c>
+      <c r="K16" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="L16" s="8">
+        <v>1</v>
+      </c>
+      <c r="M16" s="8">
         <v>1.03</v>
       </c>
     </row>
@@ -8082,7 +8257,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
@@ -8725,6 +8900,47 @@
       </c>
       <c r="M15" s="8">
         <v>0.33500000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A16" s="13">
+        <v>46141</v>
+      </c>
+      <c r="B16" s="13">
+        <v>46141</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="G16" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="H16" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="I16" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="K16" s="8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="L16" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="M16" s="8">
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>
@@ -8741,7 +8957,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
@@ -9263,6 +9479,38 @@
         <v>0.76</v>
       </c>
     </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A16" s="13">
+        <v>46141</v>
+      </c>
+      <c r="B16" s="13">
+        <v>46141</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G16" s="8">
+        <v>0.78</v>
+      </c>
+      <c r="H16" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="I16" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -9277,7 +9525,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="13" bestFit="1" customWidth="1"/>
@@ -9921,6 +10169,47 @@
         <v>8.5</v>
       </c>
       <c r="M15" s="10">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A16" s="13">
+        <v>46141</v>
+      </c>
+      <c r="B16" s="13">
+        <v>46141</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="10">
+        <v>11</v>
+      </c>
+      <c r="F16" s="10">
+        <v>10</v>
+      </c>
+      <c r="G16" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="H16" s="10">
+        <v>18.5</v>
+      </c>
+      <c r="I16" s="10">
+        <v>17</v>
+      </c>
+      <c r="J16" s="10">
+        <v>17.75</v>
+      </c>
+      <c r="K16" s="10">
+        <v>9</v>
+      </c>
+      <c r="L16" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="M16" s="10">
         <v>8.75</v>
       </c>
     </row>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1675EFCB-8535-408E-8AD5-9825D33227AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BBC1A48-3334-4C81-90E9-089185FD9749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -201,7 +201,7 @@
     <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,6 +242,14 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -266,7 +274,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -274,42 +282,45 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -327,7 +338,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -436,6 +447,9 @@
                 <c:pt idx="18">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -501,6 +515,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -604,6 +621,9 @@
                 <c:pt idx="18">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -669,6 +689,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>33</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -772,6 +795,9 @@
                 <c:pt idx="18">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -837,6 +863,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -940,6 +969,9 @@
                 <c:pt idx="18">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1004,6 +1036,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1221,7 +1256,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1330,6 +1365,9 @@
                 <c:pt idx="18">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1394,6 +1432,9 @@
                   <c:v>0.9</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>0.88</c:v>
                 </c:pt>
               </c:numCache>
@@ -1498,6 +1539,9 @@
                 <c:pt idx="18">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1562,6 +1606,9 @@
                   <c:v>1.2</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>1.18</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>1.18</c:v>
                 </c:pt>
               </c:numCache>
@@ -1666,6 +1713,9 @@
                 <c:pt idx="18">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1730,6 +1780,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>0.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -1948,7 +2001,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2057,6 +2110,9 @@
                 <c:pt idx="18">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2198,6 +2254,9 @@
                 <c:pt idx="18">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2339,6 +2398,9 @@
                 <c:pt idx="18">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2404,6 +2466,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0.315</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2484,7 +2549,7 @@
         <c:axId val="1183551503"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="0.30000000000000004"/>
+          <c:min val="0.2"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2536,7 +2601,7 @@
         <c:crossAx val="1183551023"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:majorUnit val="2.0000000000000004E-2"/>
+        <c:majorUnit val="5.000000000000001E-2"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -2622,7 +2687,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2731,6 +2796,9 @@
                 <c:pt idx="18">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2795,6 +2863,9 @@
                   <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>0.74</c:v>
                 </c:pt>
               </c:numCache>
@@ -2899,6 +2970,9 @@
                 <c:pt idx="18">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2963,6 +3037,9 @@
                   <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>0.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -3180,7 +3257,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3289,6 +3366,9 @@
                 <c:pt idx="18">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3353,6 +3433,9 @@
                   <c:v>10.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
@@ -3457,6 +3540,9 @@
                 <c:pt idx="18">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3521,6 +3607,9 @@
                   <c:v>17.75</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>16.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3625,6 +3714,9 @@
                 <c:pt idx="18">
                   <c:v>46183</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3689,6 +3781,9 @@
                   <c:v>8.75</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
@@ -7142,1073 +7237,1123 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="14" width="9" style="12"/>
-    <col min="15" max="16" width="9" style="10"/>
-    <col min="17" max="21" width="9" style="8"/>
-    <col min="22" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="12.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="9" style="14"/>
+    <col min="15" max="16" width="9" style="15"/>
+    <col min="17" max="21" width="9" style="16"/>
+    <col min="22" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" s="8" customFormat="1">
+      <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="11" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="O2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="13">
+      <c r="A3" s="11">
         <v>46043</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="11">
         <v>46043</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="12">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="6">
         <v>54</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="6">
         <v>50</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="6">
         <v>53</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="6">
         <v>52</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="6">
         <v>49</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="6">
         <v>52</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="6">
         <v>51</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="6">
         <v>50</v>
       </c>
-      <c r="M3" s="11">
+      <c r="M3" s="6">
         <v>50</v>
       </c>
-      <c r="N3" s="11">
+      <c r="N3" s="6">
         <v>22</v>
       </c>
-      <c r="O3" s="9">
+      <c r="O3" s="7">
         <v>13.1</v>
       </c>
-      <c r="P3" s="9">
+      <c r="P3" s="7">
         <v>17.5</v>
       </c>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="13">
+      <c r="A4" s="11">
         <v>46050</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="11">
         <v>46050</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="12">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="6">
         <v>54</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="6">
         <v>50</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="6">
         <v>53</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="6">
         <v>52</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="6">
         <v>49</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="6">
         <v>52</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="6">
         <v>51</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="6">
         <v>50</v>
       </c>
-      <c r="M4" s="11">
+      <c r="M4" s="6">
         <v>50</v>
       </c>
-      <c r="N4" s="11">
+      <c r="N4" s="6">
         <v>22</v>
       </c>
-      <c r="O4" s="9">
+      <c r="O4" s="7">
         <v>13.1</v>
       </c>
-      <c r="P4" s="9">
+      <c r="P4" s="7">
         <v>17.5</v>
       </c>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="13">
+      <c r="A5" s="11">
         <v>46057</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="11">
         <v>46057</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="12">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="14">
         <v>54</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="6">
         <v>50</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="14">
         <v>53</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="14">
         <v>52</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="14">
         <v>49</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="14">
         <v>52</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="14">
         <v>51</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="6">
         <v>50</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="6">
         <v>50</v>
       </c>
-      <c r="N5" s="12">
+      <c r="N5" s="14">
         <v>22</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O5" s="15">
         <v>13.1</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="13">
+      <c r="A6" s="11">
         <v>46064</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="11">
         <v>46064</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="14">
         <v>54</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="6">
         <v>50</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="14">
         <v>53</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="14">
         <v>52</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="14">
         <v>49</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="14">
         <v>52</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="14">
         <v>51</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="6">
         <v>50</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="6">
         <v>50</v>
       </c>
-      <c r="N6" s="12">
+      <c r="N6" s="14">
         <v>22</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O6" s="15">
         <v>13.1</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="13">
+      <c r="A7" s="11">
         <v>46078</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="11">
         <v>46078</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="14">
         <v>54</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="6">
         <v>50</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="14">
         <v>53</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="14">
         <v>52</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="14">
         <v>49</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="14">
         <v>52</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="14">
         <v>51</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="6">
         <v>50</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="6">
         <v>50</v>
       </c>
-      <c r="N7" s="12">
+      <c r="N7" s="14">
         <v>22</v>
       </c>
-      <c r="O7" s="10">
+      <c r="O7" s="15">
         <v>13.1</v>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="13">
+      <c r="A8" s="11">
         <v>46085</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="11">
         <v>46085</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="14">
         <v>54</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="6">
         <v>50</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="14">
         <v>53</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="14">
         <v>52</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="14">
         <v>49</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="14">
         <v>52</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="14">
         <v>51</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="6">
         <v>50</v>
       </c>
-      <c r="M8" s="11">
+      <c r="M8" s="6">
         <v>50</v>
       </c>
-      <c r="N8" s="12">
+      <c r="N8" s="14">
         <v>22</v>
       </c>
-      <c r="O8" s="10">
+      <c r="O8" s="15">
         <v>13.1</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="13">
+      <c r="A9" s="11">
         <v>46092</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="11">
         <v>46092</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="14">
         <v>53</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="14">
         <v>43</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="14">
         <v>47</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="14">
         <v>52</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="14">
         <v>42</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="14">
         <v>45</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="14">
         <v>45</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="14">
         <v>43</v>
       </c>
-      <c r="M9" s="12">
+      <c r="M9" s="14">
         <v>44</v>
       </c>
-      <c r="N9" s="12">
+      <c r="N9" s="14">
         <v>22</v>
       </c>
-      <c r="O9" s="10">
+      <c r="O9" s="15">
         <v>13.1</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="13">
+      <c r="A10" s="11">
         <v>46099</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="11">
         <v>46099</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="14">
         <v>47</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="14">
         <v>41</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="14">
         <v>45</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="14">
         <v>45</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="14">
         <v>39</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="14">
         <v>43</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="14">
         <v>42</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="14">
         <v>39</v>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="14">
         <v>40</v>
       </c>
-      <c r="N10" s="12">
+      <c r="N10" s="14">
         <v>22</v>
       </c>
-      <c r="O10" s="10">
+      <c r="O10" s="15">
         <v>13.1</v>
       </c>
-      <c r="P10" s="10">
+      <c r="P10" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="13">
+      <c r="A11" s="11">
         <v>46106</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="11">
         <v>46106</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="14">
         <v>39</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="14">
         <v>37</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="14">
         <v>39</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="14">
         <v>37</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="14">
         <v>35</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="14">
         <v>37</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="14">
         <v>37</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="14">
         <v>35</v>
       </c>
-      <c r="M11" s="12">
+      <c r="M11" s="14">
         <v>37</v>
       </c>
-      <c r="N11" s="12">
+      <c r="N11" s="14">
         <v>22</v>
       </c>
-      <c r="O11" s="10">
+      <c r="O11" s="15">
         <v>13.1</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="13">
+      <c r="A12" s="11">
         <v>46113</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="11">
         <v>46113</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="14">
         <v>39</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="14">
         <v>37</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="14">
         <v>39</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="14">
         <v>37</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="14">
         <v>35</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="14">
         <v>37</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="14">
         <v>37</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="14">
         <v>35</v>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="14">
         <v>37</v>
       </c>
-      <c r="N12" s="12">
+      <c r="N12" s="14">
         <v>22</v>
       </c>
-      <c r="O12" s="10">
+      <c r="O12" s="15">
         <v>13.1</v>
       </c>
-      <c r="P12" s="10">
+      <c r="P12" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="13">
+      <c r="A13" s="11">
         <v>46120</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="11">
         <v>46120</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="14">
         <v>39</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="14">
         <v>37</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="14">
         <v>39</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="14">
         <v>37</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="14">
         <v>35</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="14">
         <v>37</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="14">
         <v>37</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="14">
         <v>35</v>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="14">
         <v>37</v>
       </c>
-      <c r="N13" s="12">
+      <c r="N13" s="14">
         <v>22</v>
       </c>
-      <c r="O13" s="10">
+      <c r="O13" s="15">
         <v>13.1</v>
       </c>
-      <c r="P13" s="10">
+      <c r="P13" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="13">
+      <c r="A14" s="11">
         <v>46127</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="11">
         <v>46127</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="14">
         <v>39</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="14">
         <v>35</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="14">
         <v>37</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="14">
         <v>37</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="14">
         <v>33</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="14">
         <v>35</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="14">
         <v>36</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="14">
         <v>32</v>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="14">
         <v>34</v>
       </c>
-      <c r="N14" s="12">
+      <c r="N14" s="14">
         <v>22</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="15">
         <v>13.1</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="13">
+      <c r="A15" s="11">
         <v>46134</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="11">
         <v>46134</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="14">
         <v>39</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="14">
         <v>35</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="14">
         <v>37</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="14">
         <v>37</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="14">
         <v>33</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="14">
         <v>35</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="14">
         <v>36</v>
       </c>
-      <c r="L15" s="12">
+      <c r="L15" s="14">
         <v>32</v>
       </c>
-      <c r="M15" s="12">
+      <c r="M15" s="14">
         <v>34</v>
       </c>
-      <c r="N15" s="12">
+      <c r="N15" s="14">
         <v>22</v>
       </c>
-      <c r="O15" s="10">
+      <c r="O15" s="15">
         <v>13.1</v>
       </c>
-      <c r="P15" s="10">
+      <c r="P15" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="13">
+      <c r="A16" s="11">
         <v>46141</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="11">
         <v>46141</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="14">
         <v>39</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="14">
         <v>35</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="14">
         <v>37</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="14">
         <v>37</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="14">
         <v>33</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="14">
         <v>35</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="14">
         <v>36</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="14">
         <v>32</v>
       </c>
-      <c r="M16" s="12">
+      <c r="M16" s="14">
         <v>34</v>
       </c>
-      <c r="N16" s="12">
+      <c r="N16" s="14">
         <v>22</v>
       </c>
-      <c r="O16" s="10">
+      <c r="O16" s="15">
         <v>13.1</v>
       </c>
-      <c r="P16" s="10">
+      <c r="P16" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="13">
+      <c r="A17" s="11">
         <v>46155</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="11">
         <v>46155</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="14">
         <v>39</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="14">
         <v>35</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="14">
         <v>37</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="14">
         <v>37</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="14">
         <v>33</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="14">
         <v>35</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="14">
         <v>36</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="14">
         <v>32</v>
       </c>
-      <c r="M17" s="12">
+      <c r="M17" s="14">
         <v>34</v>
       </c>
-      <c r="N17" s="12">
+      <c r="N17" s="14">
         <v>22</v>
       </c>
-      <c r="O17" s="10">
+      <c r="O17" s="15">
         <v>13.1</v>
       </c>
-      <c r="P17" s="10">
+      <c r="P17" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="13">
+      <c r="A18" s="11">
         <v>46164</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="11">
         <v>46164</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="14">
         <v>39</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="14">
         <v>35</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="14">
         <v>37</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="14">
         <v>37</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="14">
         <v>33</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="14">
         <v>35</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="14">
         <v>36</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="14">
         <v>32</v>
       </c>
-      <c r="M18" s="12">
+      <c r="M18" s="14">
         <v>34</v>
       </c>
-      <c r="N18" s="12">
+      <c r="N18" s="14">
         <v>22</v>
       </c>
-      <c r="O18" s="10">
+      <c r="O18" s="15">
         <v>13.1</v>
       </c>
-      <c r="P18" s="10">
+      <c r="P18" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="13">
+      <c r="A19" s="11">
         <v>46169</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="11">
         <v>46169</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="14">
         <v>39</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="14">
         <v>35</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="14">
         <v>37</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="14">
         <v>37</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="14">
         <v>33</v>
       </c>
-      <c r="J19" s="12">
+      <c r="J19" s="14">
         <v>35</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="14">
         <v>36</v>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="14">
         <v>32</v>
       </c>
-      <c r="M19" s="12">
+      <c r="M19" s="14">
         <v>34</v>
       </c>
-      <c r="N19" s="12">
+      <c r="N19" s="14">
         <v>22</v>
       </c>
-      <c r="O19" s="10">
+      <c r="O19" s="15">
         <v>13.1</v>
       </c>
-      <c r="P19" s="10">
+      <c r="P19" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="13">
+      <c r="A20" s="11">
         <v>46176</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="11">
         <v>46176</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="14">
         <v>39</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="14">
         <v>35</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="14">
         <v>37</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="14">
         <v>37</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="14">
         <v>33</v>
       </c>
-      <c r="J20" s="12">
+      <c r="J20" s="14">
         <v>35</v>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="14">
         <v>36</v>
       </c>
-      <c r="L20" s="12">
+      <c r="L20" s="14">
         <v>32</v>
       </c>
-      <c r="M20" s="12">
+      <c r="M20" s="14">
         <v>34</v>
       </c>
-      <c r="N20" s="12">
+      <c r="N20" s="14">
         <v>22</v>
       </c>
-      <c r="O20" s="10">
+      <c r="O20" s="15">
         <v>13.1</v>
       </c>
-      <c r="P20" s="10">
+      <c r="P20" s="15">
         <v>17.5</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="13">
+      <c r="A21" s="11">
         <v>46183</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="11">
         <v>46183</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="14">
         <v>37</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="14">
         <v>35</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="14">
         <v>36</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="14">
         <v>35</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="14">
         <v>33</v>
       </c>
-      <c r="J21" s="12">
+      <c r="J21" s="14">
         <v>34</v>
       </c>
-      <c r="K21" s="12">
+      <c r="K21" s="14">
         <v>33</v>
       </c>
-      <c r="L21" s="12">
+      <c r="L21" s="14">
         <v>31</v>
       </c>
-      <c r="M21" s="12">
+      <c r="M21" s="14">
         <v>32</v>
       </c>
-      <c r="N21" s="12">
+      <c r="N21" s="14">
         <v>22</v>
       </c>
-      <c r="O21" s="10">
+      <c r="O21" s="15">
         <v>13.1</v>
       </c>
-      <c r="P21" s="10">
+      <c r="P21" s="15">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="11">
+        <v>46190</v>
+      </c>
+      <c r="B22" s="11">
+        <v>46190</v>
+      </c>
+      <c r="C22" s="12">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="14">
+        <v>36</v>
+      </c>
+      <c r="F22" s="14">
+        <v>34</v>
+      </c>
+      <c r="G22" s="14">
+        <v>35</v>
+      </c>
+      <c r="H22" s="14">
+        <v>34</v>
+      </c>
+      <c r="I22" s="14">
+        <v>32</v>
+      </c>
+      <c r="J22" s="14">
+        <v>33</v>
+      </c>
+      <c r="K22" s="14">
+        <v>32</v>
+      </c>
+      <c r="L22" s="14">
+        <v>31</v>
+      </c>
+      <c r="M22" s="14">
+        <v>31</v>
+      </c>
+      <c r="N22" s="14">
+        <v>22</v>
+      </c>
+      <c r="O22" s="15">
+        <v>13.1</v>
+      </c>
+      <c r="P22" s="15">
         <v>17.5</v>
       </c>
     </row>
@@ -8227,894 +8372,935 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="8"/>
-    <col min="22" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="16"/>
+    <col min="22" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" s="8" customFormat="1">
+      <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="4" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="13">
+      <c r="A3" s="11">
         <v>46043</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="11">
         <v>46043</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="12">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="9">
         <v>1.35</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="9">
         <v>1.25</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="9">
         <v>1.3</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="9">
         <v>1.65</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="9">
         <v>1.55</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="9">
         <v>1.6</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="9">
         <v>1.45</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="9">
         <v>1.35</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="9">
         <v>1.4</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="13">
+      <c r="A4" s="11">
         <v>46050</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="11">
         <v>46050</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="12">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="9">
         <v>1.35</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="9">
         <v>1.2</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="9">
         <v>1.3</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="9">
         <v>1.65</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="9">
         <v>1.5</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="9">
         <v>1.6</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="9">
         <v>1.45</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="9">
         <v>1.3</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="9">
         <v>1.4</v>
       </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="13">
+      <c r="A5" s="11">
         <v>46057</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="11">
         <v>46057</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="16">
         <v>1.25</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="16">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="16">
         <v>1.2</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="16">
         <v>1.55</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="16">
         <v>1.4</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="16">
         <v>1.5</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="16">
         <v>1.35</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="16">
         <v>1.2</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="16">
         <v>1.3</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="13">
+      <c r="A6" s="11">
         <v>46064</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="11">
         <v>46064</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="16">
         <v>1.25</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="16">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="16">
         <v>1.2</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="16">
         <v>1.55</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="16">
         <v>1.4</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="16">
         <v>1.5</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="16">
         <v>1.35</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="16">
         <v>1.2</v>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="16">
         <v>1.3</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="13">
+      <c r="A7" s="11">
         <v>46078</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="11">
         <v>46078</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="16">
         <v>1.25</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="16">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="16">
         <v>1.2</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="16">
         <v>1.55</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="16">
         <v>1.4</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="16">
         <v>1.5</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="16">
         <v>1.35</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="16">
         <v>1.2</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M7" s="16">
         <v>1.3</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="13">
+      <c r="A8" s="11">
         <v>46085</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="11">
         <v>46085</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="16">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="16">
         <v>1.05</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="16">
         <v>1.05</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="16">
         <v>1.4</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="16">
         <v>1.35</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="16">
         <v>1.35</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="16">
         <v>1.2</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="16">
         <v>1.1499999999999999</v>
       </c>
-      <c r="M8" s="8">
+      <c r="M8" s="16">
         <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="13">
+      <c r="A9" s="11">
         <v>46092</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="11">
         <v>46092</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="16">
         <v>1</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="16">
         <v>1.05</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="16">
         <v>1.05</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="16">
         <v>1.35</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="16">
         <v>1.33</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="16">
         <v>1.35</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="16">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="16">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="16">
         <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="13">
+      <c r="A10" s="11">
         <v>46099</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="11">
         <v>46099</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="16">
         <v>1.05</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="16">
         <v>1</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="16">
         <v>1</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="16">
         <v>1.35</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="16">
         <v>1.3</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="16">
         <v>1.3</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="16">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="16">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="16">
         <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="13">
+      <c r="A11" s="11">
         <v>46106</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="11">
         <v>46106</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="16">
         <v>1</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="16">
         <v>0.98</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="16">
         <v>1</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="16">
         <v>1.3</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="16">
         <v>1.25</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="16">
         <v>1.25</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="16">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="16">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="16">
         <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="13">
+      <c r="A12" s="11">
         <v>46113</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="11">
         <v>46113</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="16">
         <v>0.98</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="16">
         <v>0.95</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="16">
         <v>0.98</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="16">
         <v>1.3</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="16">
         <v>1.23</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="16">
         <v>1.25</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="16">
         <v>1.05</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="16">
         <v>1.02</v>
       </c>
-      <c r="M12" s="8">
+      <c r="M12" s="16">
         <v>1.05</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="13">
+      <c r="A13" s="11">
         <v>46120</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="11">
         <v>46120</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="16">
         <v>0.95</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="16">
         <v>0.9</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="16">
         <v>0.93</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="16">
         <v>1.25</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="16">
         <v>1.2</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="16">
         <v>1.23</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="16">
         <v>1.05</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="16">
         <v>1</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="16">
         <v>1.03</v>
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="13">
+      <c r="A14" s="11">
         <v>46127</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="11">
         <v>46127</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="16">
         <v>0.95</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="16">
         <v>0.9</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="16">
         <v>0.92</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="16">
         <v>1.25</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="16">
         <v>1.2</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="16">
         <v>1.23</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="16">
         <v>1.05</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="16">
         <v>1</v>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="16">
         <v>1.03</v>
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="13">
+      <c r="A15" s="11">
         <v>46134</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="11">
         <v>46134</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="16">
         <v>0.95</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="16">
         <v>0.9</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="16">
         <v>0.92</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="16">
         <v>1.25</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="16">
         <v>1.2</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="16">
         <v>1.23</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="16">
         <v>1.05</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="16">
         <v>1</v>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="16">
         <v>1.03</v>
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="13">
+      <c r="A16" s="11">
         <v>46141</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="11">
         <v>46141</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="16">
         <v>0.95</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="16">
         <v>0.9</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="16">
         <v>0.92</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="16">
         <v>1.25</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="16">
         <v>1.2</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="16">
         <v>1.23</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="16">
         <v>1.05</v>
       </c>
-      <c r="L16" s="8">
+      <c r="L16" s="16">
         <v>1</v>
       </c>
-      <c r="M16" s="8">
+      <c r="M16" s="16">
         <v>1.03</v>
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="13">
+      <c r="A17" s="11">
         <v>46155</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="11">
         <v>46155</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="16">
         <v>0.95</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="16">
         <v>0.9</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="16">
         <v>0.92</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="16">
         <v>1.25</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="16">
         <v>1.2</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="16">
         <v>1.23</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="16">
         <v>1.05</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L17" s="16">
         <v>1</v>
       </c>
-      <c r="M17" s="8">
+      <c r="M17" s="16">
         <v>1.03</v>
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="13">
+      <c r="A18" s="11">
         <v>46164</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="11">
         <v>46164</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="16">
         <v>0.95</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="16">
         <v>0.9</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="16">
         <v>0.92</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="16">
         <v>1.25</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="16">
         <v>1.2</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="16">
         <v>1.23</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="16">
         <v>1.05</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="16">
         <v>1</v>
       </c>
-      <c r="M18" s="8">
+      <c r="M18" s="16">
         <v>1.03</v>
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="13">
+      <c r="A19" s="11">
         <v>46169</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="11">
         <v>46169</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="16">
         <v>0.95</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="16">
         <v>0.9</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="16">
         <v>0.92</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="16">
         <v>1.25</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="16">
         <v>1.2</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="16">
         <v>1.23</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="16">
         <v>1.05</v>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="16">
         <v>1</v>
       </c>
-      <c r="M19" s="8">
+      <c r="M19" s="16">
         <v>1.03</v>
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="13">
+      <c r="A20" s="11">
         <v>46176</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="11">
         <v>46176</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="16">
         <v>0.9</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="16">
         <v>0.88</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="16">
         <v>0.9</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="16">
         <v>1.2</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="16">
         <v>1.18</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="16">
         <v>1.2</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20" s="16">
         <v>1</v>
       </c>
-      <c r="L20" s="8">
+      <c r="L20" s="16">
         <v>0.98</v>
       </c>
-      <c r="M20" s="8">
+      <c r="M20" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="13">
+      <c r="A21" s="11">
         <v>46183</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="11">
         <v>46183</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="16">
         <v>0.9</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="16">
         <v>0.88</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="16">
         <v>0.88</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="16">
         <v>1.2</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="16">
         <v>1.17</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="16">
         <v>1.18</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="16">
         <v>1</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="16">
         <v>0.98</v>
       </c>
-      <c r="M21" s="8">
+      <c r="M21" s="16">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="11">
+        <v>46190</v>
+      </c>
+      <c r="B22" s="11">
+        <v>46190</v>
+      </c>
+      <c r="C22" s="12">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="16">
+        <v>0.9</v>
+      </c>
+      <c r="F22" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="G22" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="H22" s="16">
+        <v>1.2</v>
+      </c>
+      <c r="I22" s="16">
+        <v>1.17</v>
+      </c>
+      <c r="J22" s="16">
+        <v>1.18</v>
+      </c>
+      <c r="K22" s="16">
+        <v>1</v>
+      </c>
+      <c r="L22" s="16">
+        <v>0.98</v>
+      </c>
+      <c r="M22" s="16">
         <v>0.98</v>
       </c>
     </row>
@@ -9132,895 +9318,936 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="8"/>
-    <col min="22" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="16"/>
+    <col min="22" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" s="8" customFormat="1">
+      <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="4" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="13">
+      <c r="A3" s="11">
         <v>46043</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="11">
         <v>46043</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="12">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="9">
         <v>0.42</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="9">
         <v>0.41</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="9">
         <v>0.41</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="9">
         <v>0.42</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="9">
         <v>0.41</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="9">
         <v>0.41</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="9">
         <v>0.42</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="9">
         <v>0.41</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="9">
         <v>0.41</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="13">
+      <c r="A4" s="11">
         <v>46050</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="11">
         <v>46050</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="12">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="9">
         <v>0.43</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="9">
         <v>0.41</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="9">
         <v>0.42</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="9">
         <v>0.43</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="9">
         <v>0.41</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="9">
         <v>0.42</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="9">
         <v>0.43</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="9">
         <v>0.41</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="9">
         <v>0.42</v>
       </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="13">
+      <c r="A5" s="11">
         <v>46057</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="11">
         <v>46057</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="16">
         <v>0.43</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="16">
         <v>0.41</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="16">
         <v>0.42</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="16">
         <v>0.43</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="16">
         <v>0.41</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="16">
         <v>0.42</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="16">
         <v>0.43</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="16">
         <v>0.41</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="16">
         <v>0.42</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="13">
+      <c r="A6" s="11">
         <v>46064</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="11">
         <v>46064</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="16">
         <v>0.43</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="16">
         <v>0.41</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="16">
         <v>0.42</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="16">
         <v>0.43</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="16">
         <v>0.41</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="16">
         <v>0.42</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="9">
         <v>0.43</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="9">
         <v>0.41</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="9">
         <v>0.42</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="13">
+      <c r="A7" s="11">
         <v>46078</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="11">
         <v>46078</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="16">
         <v>0.43</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="16">
         <v>0.41</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="16">
         <v>0.42</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="16">
         <v>0.43</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="16">
         <v>0.41</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="16">
         <v>0.42</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="16">
         <v>0.43</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="16">
         <v>0.41</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M7" s="16">
         <v>0.42</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="13">
+      <c r="A8" s="11">
         <v>46085</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="11">
         <v>46085</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="16">
         <v>0.43</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="16">
         <v>0.41</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="16">
         <v>0.42</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="16">
         <v>0.43</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="16">
         <v>0.41</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="16">
         <v>0.42</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="16">
         <v>0.43</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="16">
         <v>0.41</v>
       </c>
-      <c r="M8" s="8">
+      <c r="M8" s="16">
         <v>0.42</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="13">
+      <c r="A9" s="11">
         <v>46092</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="11">
         <v>46092</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="16">
         <v>0.42</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="16">
         <v>0.4</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="16">
         <v>0.41</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="16">
         <v>0.42</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="16">
         <v>0.4</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="16">
         <v>0.41</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="16">
         <v>0.42</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="16">
         <v>0.4</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="16">
         <v>0.41</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="13">
+      <c r="A10" s="11">
         <v>46099</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="11">
         <v>46099</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="16">
         <v>0.41</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="16">
         <v>0.39</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="16">
         <v>0.4</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="16">
         <v>0.41</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="16">
         <v>0.39</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="16">
         <v>0.4</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="16">
         <v>0.41</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="16">
         <v>0.39500000000000002</v>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="16">
         <v>0.4</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="13">
+      <c r="A11" s="11">
         <v>46106</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="11">
         <v>46106</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="16">
         <v>0.39500000000000002</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="16">
         <v>0.38</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="16">
         <v>0.39</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="16">
         <v>0.39</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="16">
         <v>0.38</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="16">
         <v>0.39</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="16">
         <v>0.39500000000000002</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="16">
         <v>0.38</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="16">
         <v>0.39</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="13">
+      <c r="A12" s="11">
         <v>46113</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="11">
         <v>46113</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="16">
         <v>0.37</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="16">
         <v>0.35</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="16">
         <v>0.36</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="16">
         <v>0.37</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="16">
         <v>0.35</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="16">
         <v>0.36</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="16">
         <v>0.37</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="16">
         <v>0.35</v>
       </c>
-      <c r="M12" s="8">
+      <c r="M12" s="16">
         <v>0.36</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="13">
+      <c r="A13" s="11">
         <v>46120</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="11">
         <v>46120</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="16">
         <v>0.36</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="16">
         <v>0.34</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="16">
         <v>0.35499999999999998</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="16">
         <v>0.36</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="16">
         <v>0.34</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="16">
         <v>0.35499999999999998</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="16">
         <v>0.36</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="16">
         <v>0.35</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="16">
         <v>0.36</v>
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="13">
+      <c r="A14" s="11">
         <v>46127</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="11">
         <v>46127</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="16">
         <v>0.34</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="16">
         <v>0.33</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="16">
         <v>0.34</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="16">
         <v>0.34</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="16">
         <v>0.33</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="16">
         <v>0.34</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="16">
         <v>0.34</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="16">
         <v>0.33</v>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="16">
         <v>0.34</v>
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="13">
+      <c r="A15" s="11">
         <v>46134</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="11">
         <v>46134</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="16">
         <v>0.34</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="16">
         <v>0.33</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="16">
         <v>0.34</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="16">
         <v>0.33</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="16">
         <v>0.34</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="16">
         <v>0.33</v>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="16">
         <v>0.33500000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="13">
+      <c r="A16" s="11">
         <v>46141</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="11">
         <v>46141</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="16">
         <v>0.33</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="16">
         <v>0.33</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="16">
         <v>0.33</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L16" s="8">
+      <c r="L16" s="16">
         <v>0.33</v>
       </c>
-      <c r="M16" s="8">
+      <c r="M16" s="16">
         <v>0.33</v>
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="13">
+      <c r="A17" s="11">
         <v>46155</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="11">
         <v>46155</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="16">
         <v>0.33</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="16">
         <v>0.33</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="16">
         <v>0.33</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L17" s="16">
         <v>0.33</v>
       </c>
-      <c r="M17" s="8">
+      <c r="M17" s="16">
         <v>0.33</v>
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="13">
+      <c r="A18" s="11">
         <v>46164</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="11">
         <v>46164</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="16">
         <v>0.33</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="16">
         <v>0.33</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="16">
         <v>0.33</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="16">
         <v>0.33</v>
       </c>
-      <c r="M18" s="8">
+      <c r="M18" s="16">
         <v>0.33</v>
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="13">
+      <c r="A19" s="11">
         <v>46169</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="11">
         <v>46169</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="16">
         <v>0.33</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="16">
         <v>0.33</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="16">
         <v>0.33</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="16">
         <v>0.33</v>
       </c>
-      <c r="M19" s="8">
+      <c r="M19" s="16">
         <v>0.33</v>
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="13">
+      <c r="A20" s="11">
         <v>46176</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="11">
         <v>46176</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="16">
         <v>0.33</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="16">
         <v>0.32500000000000001</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="16">
         <v>0.33</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="16">
         <v>0.33</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="16">
         <v>0.32500000000000001</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="16">
         <v>0.33</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20" s="16">
         <v>0.33</v>
       </c>
-      <c r="L20" s="8">
+      <c r="L20" s="16">
         <v>0.32500000000000001</v>
       </c>
-      <c r="M20" s="8">
+      <c r="M20" s="16">
         <v>0.33</v>
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="13">
+      <c r="A21" s="11">
         <v>46183</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="11">
         <v>46183</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="16">
         <v>0.31</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="16">
         <v>0.3</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="16">
         <v>0.30499999999999999</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="16">
         <v>0.32500000000000001</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="16">
         <v>0.315</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="16">
         <v>0.32</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="16">
         <v>0.32</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="16">
         <v>0.31</v>
       </c>
-      <c r="M21" s="8">
+      <c r="M21" s="16">
         <v>0.315</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="11">
+        <v>46190</v>
+      </c>
+      <c r="B22" s="11">
+        <v>46190</v>
+      </c>
+      <c r="C22" s="12">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="16">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="F22" s="16">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G22" s="16">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H22" s="16">
+        <v>0.31</v>
+      </c>
+      <c r="I22" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="J22" s="16">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="K22" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="L22" s="16">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="M22" s="16">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -10037,717 +10264,749 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="8"/>
-    <col min="22" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="10.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="16"/>
+    <col min="22" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" s="8" customFormat="1">
+      <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="4" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="13">
+      <c r="A3" s="11">
         <v>46043</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="11">
         <v>46043</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="12">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="9">
         <v>0.82</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="9">
         <v>0.78</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="9">
         <v>0.79</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="9">
         <v>0.75</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="9">
         <v>0.71</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="9">
         <v>0.72</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="13">
+      <c r="A4" s="11">
         <v>46050</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="11">
         <v>46050</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="12">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="9">
         <v>0.85</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="9">
         <v>0.78</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="9">
         <v>0.79</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="9">
         <v>0.82</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="9">
         <v>0.7</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="9">
         <v>0.76</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="13">
+      <c r="A5" s="11">
         <v>46057</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="11">
         <v>46057</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="16">
         <v>0.85</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="16">
         <v>0.78</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="16">
         <v>0.79</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="16">
         <v>0.82</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="16">
         <v>0.7</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="13">
+      <c r="A6" s="11">
         <v>46064</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="11">
         <v>46064</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="16">
         <v>0.85</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="16">
         <v>0.78</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="16">
         <v>0.79</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="16">
         <v>0.82</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="16">
         <v>0.7</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="13">
+      <c r="A7" s="11">
         <v>46078</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="11">
         <v>46078</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="16">
         <v>0.85</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="16">
         <v>0.78</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="16">
         <v>0.79</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="16">
         <v>0.82</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="16">
         <v>0.7</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="13">
+      <c r="A8" s="11">
         <v>46085</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="11">
         <v>46085</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="16">
         <v>0.85</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="16">
         <v>0.78</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="16">
         <v>0.79</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="16">
         <v>0.82</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="16">
         <v>0.7</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="13">
+      <c r="A9" s="11">
         <v>46092</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="11">
         <v>46092</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="16">
         <v>0.85</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="16">
         <v>0.78</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="16">
         <v>0.79</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="16">
         <v>0.82</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="16">
         <v>0.7</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="13">
+      <c r="A10" s="11">
         <v>46099</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="11">
         <v>46099</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="16">
         <v>0.85</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="16">
         <v>0.78</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="16">
         <v>0.79</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="16">
         <v>0.82</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="16">
         <v>0.7</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="13">
+      <c r="A11" s="11">
         <v>46106</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="11">
         <v>46106</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="16">
         <v>0.85</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="16">
         <v>0.78</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="16">
         <v>0.79</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="16">
         <v>0.82</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="16">
         <v>0.7</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="13">
+      <c r="A12" s="11">
         <v>46113</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="11">
         <v>46113</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="16">
         <v>0.85</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="16">
         <v>0.78</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="16">
         <v>0.79</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="16">
         <v>0.82</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="16">
         <v>0.7</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="13">
+      <c r="A13" s="11">
         <v>46120</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="11">
         <v>46120</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="16">
         <v>0.85</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="16">
         <v>0.78</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="16">
         <v>0.79</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="16">
         <v>0.82</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="16">
         <v>0.7</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="13">
+      <c r="A14" s="11">
         <v>46127</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="11">
         <v>46127</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="16">
         <v>0.85</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="16">
         <v>0.78</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="16">
         <v>0.79</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="16">
         <v>0.82</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="16">
         <v>0.7</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="13">
+      <c r="A15" s="11">
         <v>46134</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="11">
         <v>46134</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="16">
         <v>0.85</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="16">
         <v>0.78</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="16">
         <v>0.79</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="16">
         <v>0.82</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="16">
         <v>0.7</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="13">
+      <c r="A16" s="11">
         <v>46141</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="11">
         <v>46141</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="16">
         <v>0.8</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="16">
         <v>0.75</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="16">
         <v>0.78</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="16">
         <v>0.8</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="16">
         <v>0.75</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="13">
+      <c r="A17" s="11">
         <v>46155</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="11">
         <v>46155</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="16">
         <v>0.8</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="16">
         <v>0.75</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="16">
         <v>0.78</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="16">
         <v>0.8</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="16">
         <v>0.75</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="13">
+      <c r="A18" s="11">
         <v>46164</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="11">
         <v>46164</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="16">
         <v>0.8</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="16">
         <v>0.75</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="16">
         <v>0.78</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="16">
         <v>0.8</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="16">
         <v>0.75</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="13">
+      <c r="A19" s="11">
         <v>46169</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="11">
         <v>46169</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="16">
         <v>0.8</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="16">
         <v>0.75</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="16">
         <v>0.78</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="16">
         <v>0.8</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="16">
         <v>0.75</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="13">
+      <c r="A20" s="11">
         <v>46176</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="11">
         <v>46176</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="16">
         <v>0.78</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="16">
         <v>0.72</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="16">
         <v>0.75</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="16">
         <v>0.8</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="16">
         <v>0.75</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="16">
         <v>0.76</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="13">
+      <c r="A21" s="11">
         <v>46183</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="11">
         <v>46183</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="16">
         <v>0.75</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="16">
         <v>0.72</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="16">
         <v>0.74</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="16">
         <v>0.8</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="16">
         <v>0.75</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="16">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="11">
+        <v>46190</v>
+      </c>
+      <c r="B22" s="11">
+        <v>46190</v>
+      </c>
+      <c r="C22" s="12">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="F22" s="16">
+        <v>0.7</v>
+      </c>
+      <c r="G22" s="16">
+        <v>0.74</v>
+      </c>
+      <c r="H22" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="I22" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="J22" s="16">
         <v>0.76</v>
       </c>
     </row>
@@ -10765,896 +11024,937 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:U22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="10" customWidth="1"/>
-    <col min="6" max="13" width="9" style="10"/>
-    <col min="14" max="21" width="9" style="8"/>
-    <col min="22" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="10.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="15" customWidth="1"/>
+    <col min="6" max="13" width="9" style="15"/>
+    <col min="14" max="21" width="9" style="16"/>
+    <col min="22" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" s="8" customFormat="1">
+      <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="9" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="13">
+      <c r="A3" s="11">
         <v>46043</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="11">
         <v>46043</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="12">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="7">
         <v>12</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="7">
         <v>11</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="7">
         <v>11.5</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="7">
         <v>19</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="7">
         <v>18</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="7">
         <v>18.5</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="7">
         <v>10</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="7">
         <v>9</v>
       </c>
-      <c r="M3" s="9">
+      <c r="M3" s="7">
         <v>9.5</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="13">
+      <c r="A4" s="11">
         <v>46050</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="11">
         <v>46050</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="12">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="7">
         <v>12</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="7">
         <v>11</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="7">
         <v>11.5</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="7">
         <v>19</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="7">
         <v>18</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="7">
         <v>18.5</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="7">
         <v>10</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="7">
         <v>9</v>
       </c>
-      <c r="M4" s="9">
+      <c r="M4" s="7">
         <v>9.5</v>
       </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="13">
+      <c r="A5" s="11">
         <v>46057</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="11">
         <v>46057</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="15">
         <v>12</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="15">
         <v>11</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="15">
         <v>11.5</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="15">
         <v>19</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="15">
         <v>18</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="15">
         <v>18.5</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="15">
         <v>10</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="15">
         <v>9</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="15">
         <v>9.5</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="13">
+      <c r="A6" s="11">
         <v>46064</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="11">
         <v>46064</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="15">
         <v>12</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="15">
         <v>11</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="15">
         <v>11.5</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="15">
         <v>19</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="15">
         <v>18</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="15">
         <v>18.5</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="15">
         <v>10</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="15">
         <v>9</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="15">
         <v>9.5</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="13">
+      <c r="A7" s="11">
         <v>46078</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="11">
         <v>46078</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="15">
         <v>12</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="15">
         <v>11</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="15">
         <v>11.5</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="15">
         <v>19</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="15">
         <v>18</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="15">
         <v>18.5</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="15">
         <v>10</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="15">
         <v>9</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="15">
         <v>9.5</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="13">
+      <c r="A8" s="11">
         <v>46085</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="11">
         <v>46085</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="15">
         <v>12</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="15">
         <v>11</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="15">
         <v>11.5</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="15">
         <v>19</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="15">
         <v>18</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="15">
         <v>18.5</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="15">
         <v>10</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="15">
         <v>9</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="15">
         <v>9.5</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="13">
+      <c r="A9" s="11">
         <v>46092</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="11">
         <v>46092</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="15">
         <v>12</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="15">
         <v>11</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="15">
         <v>11.5</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="15">
         <v>19</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="15">
         <v>18</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="15">
         <v>18.5</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="15">
         <v>10</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="15">
         <v>9</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="15">
         <v>9.5</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="13">
+      <c r="A10" s="11">
         <v>46099</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="11">
         <v>46099</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="15">
         <v>12</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="15">
         <v>11</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="15">
         <v>11.5</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="15">
         <v>19</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="15">
         <v>18</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="15">
         <v>18.5</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="15">
         <v>10</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="15">
         <v>9</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="15">
         <v>9.5</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="13">
+      <c r="A11" s="11">
         <v>46106</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="11">
         <v>46106</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="15">
         <v>12</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="15">
         <v>11</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="15">
         <v>11.5</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="15">
         <v>19</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="15">
         <v>18</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="15">
         <v>18.5</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="15">
         <v>10</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="15">
         <v>9</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="15">
         <v>9.5</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="13">
+      <c r="A12" s="11">
         <v>46113</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="11">
         <v>46113</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="15">
         <v>12</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="15">
         <v>11</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="15">
         <v>11.5</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="15">
         <v>19</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="15">
         <v>18</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="15">
         <v>18.5</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="15">
         <v>10</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="15">
         <v>9</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12" s="15">
         <v>9.5</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="13">
+      <c r="A13" s="11">
         <v>46120</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="11">
         <v>46120</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="15">
         <v>11.5</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="15">
         <v>10.5</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="15">
         <v>11</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="15">
         <v>18.5</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="15">
         <v>17.5</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="15">
         <v>18</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="15">
         <v>9.5</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="15">
         <v>8.5</v>
       </c>
-      <c r="M13" s="10">
+      <c r="M13" s="15">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="13">
+      <c r="A14" s="11">
         <v>46127</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="11">
         <v>46127</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="15">
         <v>11</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="15">
         <v>10</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="15">
         <v>10.5</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="15">
         <v>18.5</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="15">
         <v>17</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="15">
         <v>17.75</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="15">
         <v>9</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="15">
         <v>8.5</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="15">
         <v>8.75</v>
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="13">
+      <c r="A15" s="11">
         <v>46134</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="11">
         <v>46134</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="15">
         <v>11</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="15">
         <v>10</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="15">
         <v>10.5</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="15">
         <v>18.5</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="15">
         <v>17</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="15">
         <v>17.75</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="15">
         <v>9</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="15">
         <v>8.5</v>
       </c>
-      <c r="M15" s="10">
+      <c r="M15" s="15">
         <v>8.75</v>
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="13">
+      <c r="A16" s="11">
         <v>46141</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="11">
         <v>46141</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="15">
         <v>11</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="15">
         <v>10</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="15">
         <v>10.5</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="15">
         <v>18.5</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="15">
         <v>17</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="15">
         <v>17.75</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="15">
         <v>9</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L16" s="15">
         <v>8.5</v>
       </c>
-      <c r="M16" s="10">
+      <c r="M16" s="15">
         <v>8.75</v>
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="13">
+      <c r="A17" s="11">
         <v>46155</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="11">
         <v>46155</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="15">
         <v>11</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="15">
         <v>10</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="15">
         <v>10.5</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="15">
         <v>18.5</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="15">
         <v>17</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="15">
         <v>17.75</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="15">
         <v>9</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="15">
         <v>8.5</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="15">
         <v>8.75</v>
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="13">
+      <c r="A18" s="11">
         <v>46164</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="11">
         <v>46164</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="15">
         <v>11</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="15">
         <v>10</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="15">
         <v>10.5</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="15">
         <v>18.5</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="15">
         <v>17</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="15">
         <v>17.75</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="15">
         <v>9</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="15">
         <v>8.5</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="15">
         <v>8.75</v>
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="13">
+      <c r="A19" s="11">
         <v>46169</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="11">
         <v>46169</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="15">
         <v>11</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="15">
         <v>10</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="15">
         <v>10.5</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="15">
         <v>18.5</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="15">
         <v>17</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="15">
         <v>17.75</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="15">
         <v>9</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="15">
         <v>8.5</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="15">
         <v>8.75</v>
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="13">
+      <c r="A20" s="11">
         <v>46176</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="11">
         <v>46176</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="15">
         <v>11</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="15">
         <v>10</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="15">
         <v>10.5</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="15">
         <v>18.5</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="15">
         <v>17</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="15">
         <v>17.75</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="15">
         <v>9</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="15">
         <v>8.5</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="15">
         <v>8.75</v>
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="13">
+      <c r="A21" s="11">
         <v>46183</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="11">
         <v>46183</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="12">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="15">
         <v>10.5</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="15">
         <v>9.5</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="15">
         <v>10</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="15">
         <v>17</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="15">
         <v>16</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="15">
         <v>16.5</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="15">
         <v>8.5</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="15">
         <v>8</v>
       </c>
-      <c r="M21" s="10">
+      <c r="M21" s="15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="11">
+        <v>46190</v>
+      </c>
+      <c r="B22" s="11">
+        <v>46190</v>
+      </c>
+      <c r="C22" s="12">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="F22" s="15">
+        <v>9.5</v>
+      </c>
+      <c r="G22" s="15">
+        <v>10</v>
+      </c>
+      <c r="H22" s="15">
+        <v>17</v>
+      </c>
+      <c r="I22" s="15">
+        <v>16</v>
+      </c>
+      <c r="J22" s="15">
+        <v>16.5</v>
+      </c>
+      <c r="K22" s="15">
+        <v>8.5</v>
+      </c>
+      <c r="L22" s="15">
+        <v>8</v>
+      </c>
+      <c r="M22" s="15">
         <v>8</v>
       </c>
     </row>
@@ -11673,7 +11973,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9750F8-1F5B-4526-B393-530CBB79CB33}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11685,9 +11985,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/PV.xlsx
+++ b/data/industry/TrendForce/PV.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BBC1A48-3334-4C81-90E9-089185FD9749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D57E72-0E97-4AD9-B310-CB1FB782857C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -274,12 +274,37 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -291,36 +316,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -338,7 +337,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -450,6 +449,9 @@
                 <c:pt idx="19">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -518,6 +520,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>33.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -624,6 +629,9 @@
                 <c:pt idx="19">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -692,6 +700,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>32.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -798,6 +809,9 @@
                 <c:pt idx="19">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -865,6 +879,9 @@
                   <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
@@ -972,6 +989,9 @@
                 <c:pt idx="19">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1039,6 +1059,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1256,7 +1279,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1368,6 +1391,9 @@
                 <c:pt idx="19">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1435,6 +1461,9 @@
                   <c:v>0.88</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>0.88</c:v>
                 </c:pt>
               </c:numCache>
@@ -1542,6 +1571,9 @@
                 <c:pt idx="19">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1609,6 +1641,9 @@
                   <c:v>1.18</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>1.18</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1.18</c:v>
                 </c:pt>
               </c:numCache>
@@ -1716,6 +1751,9 @@
                 <c:pt idx="19">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1783,6 +1821,9 @@
                   <c:v>0.98</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>0.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -2001,7 +2042,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2113,6 +2154,9 @@
                 <c:pt idx="19">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2257,6 +2301,9 @@
                 <c:pt idx="19">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2401,6 +2448,9 @@
                 <c:pt idx="19">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2469,6 +2519,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.29499999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2687,7 +2740,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2799,6 +2852,9 @@
                 <c:pt idx="19">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2867,6 +2923,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.73</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2973,6 +3032,9 @@
                 <c:pt idx="19">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3040,6 +3102,9 @@
                   <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>0.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -3257,7 +3322,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3369,6 +3434,9 @@
                 <c:pt idx="19">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3436,6 +3504,9 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
@@ -3543,6 +3614,9 @@
                 <c:pt idx="19">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3610,6 +3684,9 @@
                   <c:v>16.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>16.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3717,6 +3794,9 @@
                 <c:pt idx="19">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3784,6 +3864,9 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
@@ -7237,1123 +7320,1172 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:U23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="14" width="9" style="14"/>
-    <col min="15" max="16" width="9" style="15"/>
-    <col min="17" max="21" width="9" style="16"/>
-    <col min="22" max="16384" width="9" style="10"/>
+    <col min="1" max="1" width="12.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="9" style="10"/>
+    <col min="15" max="16" width="9" style="11"/>
+    <col min="17" max="21" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="8" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:21" s="5" customFormat="1">
+      <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6" t="s">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="11">
+      <c r="A3" s="7">
         <v>46043</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="7">
         <v>46043</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="3">
         <v>54</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="3">
         <v>50</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="3">
         <v>53</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="3">
         <v>52</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="3">
         <v>49</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="3">
         <v>52</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="3">
         <v>51</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="3">
         <v>50</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="3">
         <v>50</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="3">
         <v>22</v>
       </c>
-      <c r="O3" s="7">
+      <c r="O3" s="4">
         <v>13.1</v>
       </c>
-      <c r="P3" s="7">
+      <c r="P3" s="4">
         <v>17.5</v>
       </c>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="11">
+      <c r="A4" s="7">
         <v>46050</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="7">
         <v>46050</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>54</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>50</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>53</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="3">
         <v>52</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="3">
         <v>49</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>52</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="3">
         <v>51</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="3">
         <v>50</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="3">
         <v>50</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="3">
         <v>22</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="4">
         <v>13.1</v>
       </c>
-      <c r="P4" s="7">
+      <c r="P4" s="4">
         <v>17.5</v>
       </c>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="11">
+      <c r="A5" s="7">
         <v>46057</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="7">
         <v>46057</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="10">
         <v>54</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="3">
         <v>50</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="10">
         <v>53</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="10">
         <v>52</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="10">
         <v>49</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="10">
         <v>52</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="10">
         <v>51</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="3">
         <v>50</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="3">
         <v>50</v>
       </c>
-      <c r="N5" s="14">
+      <c r="N5" s="10">
         <v>22</v>
       </c>
-      <c r="O5" s="15">
+      <c r="O5" s="11">
         <v>13.1</v>
       </c>
-      <c r="P5" s="15">
+      <c r="P5" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="11">
+      <c r="A6" s="7">
         <v>46064</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="7">
         <v>46064</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="10">
         <v>54</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="3">
         <v>50</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="10">
         <v>53</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="10">
         <v>52</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="10">
         <v>49</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="10">
         <v>52</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="10">
         <v>51</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="3">
         <v>50</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="3">
         <v>50</v>
       </c>
-      <c r="N6" s="14">
+      <c r="N6" s="10">
         <v>22</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6" s="11">
         <v>13.1</v>
       </c>
-      <c r="P6" s="15">
+      <c r="P6" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="11">
+      <c r="A7" s="7">
         <v>46078</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="7">
         <v>46078</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="10">
         <v>54</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="3">
         <v>50</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="10">
         <v>53</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="10">
         <v>52</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="10">
         <v>49</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="10">
         <v>52</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="10">
         <v>51</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="3">
         <v>50</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="3">
         <v>50</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="10">
         <v>22</v>
       </c>
-      <c r="O7" s="15">
+      <c r="O7" s="11">
         <v>13.1</v>
       </c>
-      <c r="P7" s="15">
+      <c r="P7" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="11">
+      <c r="A8" s="7">
         <v>46085</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="7">
         <v>46085</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="10">
         <v>54</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="3">
         <v>50</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="10">
         <v>53</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="10">
         <v>52</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="10">
         <v>49</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="10">
         <v>52</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="10">
         <v>51</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="3">
         <v>50</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="3">
         <v>50</v>
       </c>
-      <c r="N8" s="14">
+      <c r="N8" s="10">
         <v>22</v>
       </c>
-      <c r="O8" s="15">
+      <c r="O8" s="11">
         <v>13.1</v>
       </c>
-      <c r="P8" s="15">
+      <c r="P8" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="11">
+      <c r="A9" s="7">
         <v>46092</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="7">
         <v>46092</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="10">
         <v>53</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="10">
         <v>43</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="10">
         <v>47</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="10">
         <v>52</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="10">
         <v>42</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="10">
         <v>45</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="10">
         <v>45</v>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="10">
         <v>43</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="10">
         <v>44</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="10">
         <v>22</v>
       </c>
-      <c r="O9" s="15">
+      <c r="O9" s="11">
         <v>13.1</v>
       </c>
-      <c r="P9" s="15">
+      <c r="P9" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="11">
+      <c r="A10" s="7">
         <v>46099</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="7">
         <v>46099</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="10">
         <v>47</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="10">
         <v>41</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="10">
         <v>45</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="10">
         <v>45</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="10">
         <v>39</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="10">
         <v>43</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="10">
         <v>42</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="10">
         <v>39</v>
       </c>
-      <c r="M10" s="14">
+      <c r="M10" s="10">
         <v>40</v>
       </c>
-      <c r="N10" s="14">
+      <c r="N10" s="10">
         <v>22</v>
       </c>
-      <c r="O10" s="15">
+      <c r="O10" s="11">
         <v>13.1</v>
       </c>
-      <c r="P10" s="15">
+      <c r="P10" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="11">
+      <c r="A11" s="7">
         <v>46106</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="7">
         <v>46106</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="10">
         <v>39</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="10">
         <v>37</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="10">
         <v>39</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="10">
         <v>37</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="10">
         <v>35</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="10">
         <v>37</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="10">
         <v>37</v>
       </c>
-      <c r="L11" s="14">
+      <c r="L11" s="10">
         <v>35</v>
       </c>
-      <c r="M11" s="14">
+      <c r="M11" s="10">
         <v>37</v>
       </c>
-      <c r="N11" s="14">
+      <c r="N11" s="10">
         <v>22</v>
       </c>
-      <c r="O11" s="15">
+      <c r="O11" s="11">
         <v>13.1</v>
       </c>
-      <c r="P11" s="15">
+      <c r="P11" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="11">
+      <c r="A12" s="7">
         <v>46113</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="7">
         <v>46113</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="10">
         <v>39</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="10">
         <v>37</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="10">
         <v>39</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="10">
         <v>37</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="10">
         <v>35</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="10">
         <v>37</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="10">
         <v>37</v>
       </c>
-      <c r="L12" s="14">
+      <c r="L12" s="10">
         <v>35</v>
       </c>
-      <c r="M12" s="14">
+      <c r="M12" s="10">
         <v>37</v>
       </c>
-      <c r="N12" s="14">
+      <c r="N12" s="10">
         <v>22</v>
       </c>
-      <c r="O12" s="15">
+      <c r="O12" s="11">
         <v>13.1</v>
       </c>
-      <c r="P12" s="15">
+      <c r="P12" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="11">
+      <c r="A13" s="7">
         <v>46120</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="7">
         <v>46120</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="10">
         <v>39</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="10">
         <v>37</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="10">
         <v>39</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="10">
         <v>37</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="10">
         <v>35</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="10">
         <v>37</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="10">
         <v>37</v>
       </c>
-      <c r="L13" s="14">
+      <c r="L13" s="10">
         <v>35</v>
       </c>
-      <c r="M13" s="14">
+      <c r="M13" s="10">
         <v>37</v>
       </c>
-      <c r="N13" s="14">
+      <c r="N13" s="10">
         <v>22</v>
       </c>
-      <c r="O13" s="15">
+      <c r="O13" s="11">
         <v>13.1</v>
       </c>
-      <c r="P13" s="15">
+      <c r="P13" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="11">
+      <c r="A14" s="7">
         <v>46127</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="7">
         <v>46127</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="10">
         <v>39</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="10">
         <v>35</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="10">
         <v>37</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="10">
         <v>37</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="10">
         <v>33</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="10">
         <v>35</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="10">
         <v>36</v>
       </c>
-      <c r="L14" s="14">
+      <c r="L14" s="10">
         <v>32</v>
       </c>
-      <c r="M14" s="14">
+      <c r="M14" s="10">
         <v>34</v>
       </c>
-      <c r="N14" s="14">
+      <c r="N14" s="10">
         <v>22</v>
       </c>
-      <c r="O14" s="15">
+      <c r="O14" s="11">
         <v>13.1</v>
       </c>
-      <c r="P14" s="15">
+      <c r="P14" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="11">
+      <c r="A15" s="7">
         <v>46134</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="7">
         <v>46134</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="10">
         <v>39</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="10">
         <v>35</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="10">
         <v>37</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="10">
         <v>37</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="10">
         <v>33</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="10">
         <v>35</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="10">
         <v>36</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="10">
         <v>32</v>
       </c>
-      <c r="M15" s="14">
+      <c r="M15" s="10">
         <v>34</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="10">
         <v>22</v>
       </c>
-      <c r="O15" s="15">
+      <c r="O15" s="11">
         <v>13.1</v>
       </c>
-      <c r="P15" s="15">
+      <c r="P15" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="11">
+      <c r="A16" s="7">
         <v>46141</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="7">
         <v>46141</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="10">
         <v>39</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="10">
         <v>35</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="10">
         <v>37</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="10">
         <v>37</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="10">
         <v>33</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="10">
         <v>35</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="10">
         <v>36</v>
       </c>
-      <c r="L16" s="14">
+      <c r="L16" s="10">
         <v>32</v>
       </c>
-      <c r="M16" s="14">
+      <c r="M16" s="10">
         <v>34</v>
       </c>
-      <c r="N16" s="14">
+      <c r="N16" s="10">
         <v>22</v>
       </c>
-      <c r="O16" s="15">
+      <c r="O16" s="11">
         <v>13.1</v>
       </c>
-      <c r="P16" s="15">
+      <c r="P16" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="11">
+      <c r="A17" s="7">
         <v>46155</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="7">
         <v>46155</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="10">
         <v>39</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="10">
         <v>35</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="10">
         <v>37</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="10">
         <v>37</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="10">
         <v>33</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="10">
         <v>35</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="10">
         <v>36</v>
       </c>
-      <c r="L17" s="14">
+      <c r="L17" s="10">
         <v>32</v>
       </c>
-      <c r="M17" s="14">
+      <c r="M17" s="10">
         <v>34</v>
       </c>
-      <c r="N17" s="14">
+      <c r="N17" s="10">
         <v>22</v>
       </c>
-      <c r="O17" s="15">
+      <c r="O17" s="11">
         <v>13.1</v>
       </c>
-      <c r="P17" s="15">
+      <c r="P17" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="11">
+      <c r="A18" s="7">
         <v>46164</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="7">
         <v>46164</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="10">
         <v>39</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="10">
         <v>35</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="10">
         <v>37</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="10">
         <v>37</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="10">
         <v>33</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="10">
         <v>35</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="10">
         <v>36</v>
       </c>
-      <c r="L18" s="14">
+      <c r="L18" s="10">
         <v>32</v>
       </c>
-      <c r="M18" s="14">
+      <c r="M18" s="10">
         <v>34</v>
       </c>
-      <c r="N18" s="14">
+      <c r="N18" s="10">
         <v>22</v>
       </c>
-      <c r="O18" s="15">
+      <c r="O18" s="11">
         <v>13.1</v>
       </c>
-      <c r="P18" s="15">
+      <c r="P18" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="11">
+      <c r="A19" s="7">
         <v>46169</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="7">
         <v>46169</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="10">
         <v>39</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="10">
         <v>35</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="10">
         <v>37</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="10">
         <v>37</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="10">
         <v>33</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="10">
         <v>35</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="10">
         <v>36</v>
       </c>
-      <c r="L19" s="14">
+      <c r="L19" s="10">
         <v>32</v>
       </c>
-      <c r="M19" s="14">
+      <c r="M19" s="10">
         <v>34</v>
       </c>
-      <c r="N19" s="14">
+      <c r="N19" s="10">
         <v>22</v>
       </c>
-      <c r="O19" s="15">
+      <c r="O19" s="11">
         <v>13.1</v>
       </c>
-      <c r="P19" s="15">
+      <c r="P19" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="11">
+      <c r="A20" s="7">
         <v>46176</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="7">
         <v>46176</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="10">
         <v>39</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="10">
         <v>35</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="10">
         <v>37</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="10">
         <v>37</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="10">
         <v>33</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="10">
         <v>35</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="10">
         <v>36</v>
       </c>
-      <c r="L20" s="14">
+      <c r="L20" s="10">
         <v>32</v>
       </c>
-      <c r="M20" s="14">
+      <c r="M20" s="10">
         <v>34</v>
       </c>
-      <c r="N20" s="14">
+      <c r="N20" s="10">
         <v>22</v>
       </c>
-      <c r="O20" s="15">
+      <c r="O20" s="11">
         <v>13.1</v>
       </c>
-      <c r="P20" s="15">
+      <c r="P20" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="11">
+      <c r="A21" s="7">
         <v>46183</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="7">
         <v>46183</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="10">
         <v>37</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="10">
         <v>35</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="10">
         <v>36</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="10">
         <v>35</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="10">
         <v>33</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="10">
         <v>34</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="10">
         <v>33</v>
       </c>
-      <c r="L21" s="14">
+      <c r="L21" s="10">
         <v>31</v>
       </c>
-      <c r="M21" s="14">
+      <c r="M21" s="10">
         <v>32</v>
       </c>
-      <c r="N21" s="14">
+      <c r="N21" s="10">
         <v>22</v>
       </c>
-      <c r="O21" s="15">
+      <c r="O21" s="11">
         <v>13.1</v>
       </c>
-      <c r="P21" s="15">
+      <c r="P21" s="11">
         <v>17.5</v>
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="11">
+      <c r="A22" s="7">
         <v>46190</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="7">
         <v>46190</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="10">
         <v>36</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="10">
         <v>34</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="10">
         <v>35</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="10">
         <v>34</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="10">
         <v>32</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="10">
         <v>33</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="10">
         <v>32</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="10">
         <v>31</v>
       </c>
-      <c r="M22" s="14">
+      <c r="M22" s="10">
         <v>31</v>
       </c>
-      <c r="N22" s="14">
+      <c r="N22" s="10">
         <v>22</v>
       </c>
-      <c r="O22" s="15">
+      <c r="O22" s="11">
         <v>13.1</v>
       </c>
-      <c r="P22" s="15">
+      <c r="P22" s="11">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="7">
+        <v>46197</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46197</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="10">
+        <v>34</v>
+      </c>
+      <c r="F23" s="10">
+        <v>33</v>
+      </c>
+      <c r="G23" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="H23" s="10">
+        <v>33</v>
+      </c>
+      <c r="I23" s="10">
+        <v>32</v>
+      </c>
+      <c r="J23" s="10">
+        <v>32.5</v>
+      </c>
+      <c r="K23" s="10">
+        <v>32</v>
+      </c>
+      <c r="L23" s="10">
+        <v>30</v>
+      </c>
+      <c r="M23" s="10">
+        <v>31</v>
+      </c>
+      <c r="N23" s="10">
+        <v>22</v>
+      </c>
+      <c r="O23" s="11">
+        <v>13.1</v>
+      </c>
+      <c r="P23" s="11">
         <v>17.5</v>
       </c>
     </row>
@@ -8372,935 +8504,975 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:U23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="16"/>
-    <col min="22" max="16384" width="9" style="10"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="8" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:21" s="5" customFormat="1">
+      <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="9" t="s">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="11">
+      <c r="A3" s="7">
         <v>46043</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="7">
         <v>46043</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="6">
         <v>1.35</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="6">
         <v>1.25</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="6">
         <v>1.3</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="6">
         <v>1.65</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="6">
         <v>1.55</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="6">
         <v>1.6</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="6">
         <v>1.45</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="6">
         <v>1.35</v>
       </c>
-      <c r="M3" s="9">
+      <c r="M3" s="6">
         <v>1.4</v>
       </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="11">
+      <c r="A4" s="7">
         <v>46050</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="7">
         <v>46050</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="6">
         <v>1.35</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="6">
         <v>1.2</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="6">
         <v>1.3</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="6">
         <v>1.65</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="6">
         <v>1.5</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="6">
         <v>1.6</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="6">
         <v>1.45</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="6">
         <v>1.3</v>
       </c>
-      <c r="M4" s="9">
+      <c r="M4" s="6">
         <v>1.4</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="11">
+      <c r="A5" s="7">
         <v>46057</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="7">
         <v>46057</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="12">
         <v>1.25</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="12">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="12">
         <v>1.2</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="12">
         <v>1.55</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="12">
         <v>1.4</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="12">
         <v>1.5</v>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="12">
         <v>1.35</v>
       </c>
-      <c r="L5" s="16">
+      <c r="L5" s="12">
         <v>1.2</v>
       </c>
-      <c r="M5" s="16">
+      <c r="M5" s="12">
         <v>1.3</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="11">
+      <c r="A6" s="7">
         <v>46064</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="7">
         <v>46064</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="12">
         <v>1.25</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="12">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="12">
         <v>1.2</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="12">
         <v>1.55</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="12">
         <v>1.4</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="12">
         <v>1.5</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="12">
         <v>1.35</v>
       </c>
-      <c r="L6" s="16">
+      <c r="L6" s="12">
         <v>1.2</v>
       </c>
-      <c r="M6" s="16">
+      <c r="M6" s="12">
         <v>1.3</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="11">
+      <c r="A7" s="7">
         <v>46078</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="7">
         <v>46078</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="12">
         <v>1.25</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="12">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="12">
         <v>1.2</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="12">
         <v>1.55</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="12">
         <v>1.4</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="12">
         <v>1.5</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="12">
         <v>1.35</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="12">
         <v>1.2</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="12">
         <v>1.3</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="11">
+      <c r="A8" s="7">
         <v>46085</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="7">
         <v>46085</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="12">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="12">
         <v>1.05</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="12">
         <v>1.05</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="12">
         <v>1.4</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="12">
         <v>1.35</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="12">
         <v>1.35</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="12">
         <v>1.2</v>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="12">
         <v>1.1499999999999999</v>
       </c>
-      <c r="M8" s="16">
+      <c r="M8" s="12">
         <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="11">
+      <c r="A9" s="7">
         <v>46092</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="7">
         <v>46092</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="12">
         <v>1</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="12">
         <v>1.05</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="12">
         <v>1.05</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="12">
         <v>1.35</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="12">
         <v>1.33</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="12">
         <v>1.35</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="12">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L9" s="16">
+      <c r="L9" s="12">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="12">
         <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="11">
+      <c r="A10" s="7">
         <v>46099</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="7">
         <v>46099</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="12">
         <v>1.05</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="12">
         <v>1</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="12">
         <v>1</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="12">
         <v>1.35</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="12">
         <v>1.3</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="12">
         <v>1.3</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="12">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="12">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="12">
         <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="11">
+      <c r="A11" s="7">
         <v>46106</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="7">
         <v>46106</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="12">
         <v>1</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="12">
         <v>0.98</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="12">
         <v>1</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="12">
         <v>1.3</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="12">
         <v>1.25</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="12">
         <v>1.25</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="12">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="12">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="12">
         <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="11">
+      <c r="A12" s="7">
         <v>46113</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="7">
         <v>46113</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="12">
         <v>0.98</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="12">
         <v>0.95</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="12">
         <v>0.98</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="12">
         <v>1.3</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="12">
         <v>1.23</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="12">
         <v>1.25</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="12">
         <v>1.05</v>
       </c>
-      <c r="L12" s="16">
+      <c r="L12" s="12">
         <v>1.02</v>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="12">
         <v>1.05</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="11">
+      <c r="A13" s="7">
         <v>46120</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="7">
         <v>46120</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="12">
         <v>0.95</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="12">
         <v>0.9</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="12">
         <v>0.93</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="12">
         <v>1.25</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="12">
         <v>1.2</v>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="12">
         <v>1.23</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="12">
         <v>1.05</v>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="12">
         <v>1</v>
       </c>
-      <c r="M13" s="16">
+      <c r="M13" s="12">
         <v>1.03</v>
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="11">
+      <c r="A14" s="7">
         <v>46127</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="7">
         <v>46127</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="12">
         <v>0.95</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="12">
         <v>0.9</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="12">
         <v>0.92</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="12">
         <v>1.25</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="12">
         <v>1.2</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="12">
         <v>1.23</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="12">
         <v>1.05</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="12">
         <v>1</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="12">
         <v>1.03</v>
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="11">
+      <c r="A15" s="7">
         <v>46134</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="7">
         <v>46134</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="12">
         <v>0.95</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="12">
         <v>0.9</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="12">
         <v>0.92</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="12">
         <v>1.25</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="12">
         <v>1.2</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="12">
         <v>1.23</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="12">
         <v>1.05</v>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="12">
         <v>1</v>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="12">
         <v>1.03</v>
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="11">
+      <c r="A16" s="7">
         <v>46141</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="7">
         <v>46141</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="12">
         <v>0.95</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="12">
         <v>0.9</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="12">
         <v>0.92</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="12">
         <v>1.25</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="12">
         <v>1.2</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="12">
         <v>1.23</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="12">
         <v>1.05</v>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="12">
         <v>1</v>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="12">
         <v>1.03</v>
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="11">
+      <c r="A17" s="7">
         <v>46155</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="7">
         <v>46155</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="12">
         <v>0.95</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="12">
         <v>0.9</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="12">
         <v>0.92</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="12">
         <v>1.25</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="12">
         <v>1.2</v>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="12">
         <v>1.23</v>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="12">
         <v>1.05</v>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="12">
         <v>1</v>
       </c>
-      <c r="M17" s="16">
+      <c r="M17" s="12">
         <v>1.03</v>
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="11">
+      <c r="A18" s="7">
         <v>46164</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="7">
         <v>46164</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="12">
         <v>0.95</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="12">
         <v>0.9</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="12">
         <v>0.92</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="12">
         <v>1.25</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="12">
         <v>1.2</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="12">
         <v>1.23</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="12">
         <v>1.05</v>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="12">
         <v>1</v>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="12">
         <v>1.03</v>
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="11">
+      <c r="A19" s="7">
         <v>46169</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="7">
         <v>46169</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="12">
         <v>0.95</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="12">
         <v>0.9</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="12">
         <v>0.92</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="12">
         <v>1.25</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="12">
         <v>1.2</v>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="12">
         <v>1.23</v>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="12">
         <v>1.05</v>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="12">
         <v>1</v>
       </c>
-      <c r="M19" s="16">
+      <c r="M19" s="12">
         <v>1.03</v>
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="11">
+      <c r="A20" s="7">
         <v>46176</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="7">
         <v>46176</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="12">
         <v>0.9</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="12">
         <v>0.88</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="12">
         <v>0.9</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="12">
         <v>1.2</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="12">
         <v>1.18</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="12">
         <v>1.2</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="12">
         <v>1</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="12">
         <v>0.98</v>
       </c>
-      <c r="M20" s="16">
+      <c r="M20" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="11">
+      <c r="A21" s="7">
         <v>46183</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="7">
         <v>46183</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="12">
         <v>0.9</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="12">
         <v>0.88</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="12">
         <v>0.88</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="12">
         <v>1.2</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="12">
         <v>1.17</v>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="12">
         <v>1.18</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="12">
         <v>1</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="12">
         <v>0.98</v>
       </c>
-      <c r="M21" s="16">
+      <c r="M21" s="12">
         <v>0.98</v>
       </c>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="11">
+      <c r="A22" s="7">
         <v>46190</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="7">
         <v>46190</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="12">
         <v>0.9</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="12">
         <v>0.88</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="12">
         <v>0.88</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="12">
         <v>1.2</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="12">
         <v>1.17</v>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="12">
         <v>1.18</v>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="12">
         <v>1</v>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="12">
         <v>0.98</v>
       </c>
-      <c r="M22" s="16">
+      <c r="M22" s="12">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="7">
+        <v>46197</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46197</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="F23" s="12">
+        <v>0.88</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0.88</v>
+      </c>
+      <c r="H23" s="12">
+        <v>1.2</v>
+      </c>
+      <c r="I23" s="12">
+        <v>1.17</v>
+      </c>
+      <c r="J23" s="12">
+        <v>1.18</v>
+      </c>
+      <c r="K23" s="12">
+        <v>1</v>
+      </c>
+      <c r="L23" s="12">
+        <v>0.98</v>
+      </c>
+      <c r="M23" s="12">
         <v>0.98</v>
       </c>
     </row>
@@ -9318,936 +9490,976 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:U23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="16"/>
-    <col min="22" max="16384" width="9" style="10"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="8" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:21" s="5" customFormat="1">
+      <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="M1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="9" t="s">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="11">
+      <c r="A3" s="7">
         <v>46043</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="7">
         <v>46043</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="6">
         <v>0.42</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="6">
         <v>0.41</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="6">
         <v>0.41</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="6">
         <v>0.42</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="6">
         <v>0.41</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="6">
         <v>0.41</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="6">
         <v>0.42</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="6">
         <v>0.41</v>
       </c>
-      <c r="M3" s="9">
+      <c r="M3" s="6">
         <v>0.41</v>
       </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="11">
+      <c r="A4" s="7">
         <v>46050</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="7">
         <v>46050</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="6">
         <v>0.43</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="6">
         <v>0.41</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="6">
         <v>0.42</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="6">
         <v>0.43</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="6">
         <v>0.41</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="6">
         <v>0.42</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="6">
         <v>0.43</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="6">
         <v>0.41</v>
       </c>
-      <c r="M4" s="9">
+      <c r="M4" s="6">
         <v>0.42</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="11">
+      <c r="A5" s="7">
         <v>46057</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="7">
         <v>46057</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="12">
         <v>0.43</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="12">
         <v>0.41</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="12">
         <v>0.42</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="12">
         <v>0.43</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="12">
         <v>0.41</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="12">
         <v>0.42</v>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="12">
         <v>0.43</v>
       </c>
-      <c r="L5" s="16">
+      <c r="L5" s="12">
         <v>0.41</v>
       </c>
-      <c r="M5" s="16">
+      <c r="M5" s="12">
         <v>0.42</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="11">
+      <c r="A6" s="7">
         <v>46064</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="7">
         <v>46064</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="12">
         <v>0.43</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="12">
         <v>0.41</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="12">
         <v>0.42</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="12">
         <v>0.43</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="12">
         <v>0.41</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="12">
         <v>0.42</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="6">
         <v>0.43</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="6">
         <v>0.41</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="6">
         <v>0.42</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="11">
+      <c r="A7" s="7">
         <v>46078</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="7">
         <v>46078</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="12">
         <v>0.43</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="12">
         <v>0.41</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="12">
         <v>0.42</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="12">
         <v>0.43</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="12">
         <v>0.41</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="12">
         <v>0.42</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="12">
         <v>0.43</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="12">
         <v>0.41</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="12">
         <v>0.42</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="11">
+      <c r="A8" s="7">
         <v>46085</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="7">
         <v>46085</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="12">
         <v>0.43</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="12">
         <v>0.41</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="12">
         <v>0.42</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="12">
         <v>0.43</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="12">
         <v>0.41</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="12">
         <v>0.42</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="12">
         <v>0.43</v>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="12">
         <v>0.41</v>
       </c>
-      <c r="M8" s="16">
+      <c r="M8" s="12">
         <v>0.42</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="11">
+      <c r="A9" s="7">
         <v>46092</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="7">
         <v>46092</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="12">
         <v>0.42</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="12">
         <v>0.4</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="12">
         <v>0.41</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="12">
         <v>0.42</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="12">
         <v>0.4</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="12">
         <v>0.41</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="12">
         <v>0.42</v>
       </c>
-      <c r="L9" s="16">
+      <c r="L9" s="12">
         <v>0.4</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="12">
         <v>0.41</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="11">
+      <c r="A10" s="7">
         <v>46099</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="7">
         <v>46099</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="12">
         <v>0.41</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="12">
         <v>0.39</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="12">
         <v>0.4</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="12">
         <v>0.41</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="12">
         <v>0.39</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="12">
         <v>0.4</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="12">
         <v>0.41</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="12">
         <v>0.39500000000000002</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="12">
         <v>0.4</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="11">
+      <c r="A11" s="7">
         <v>46106</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="7">
         <v>46106</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="12">
         <v>0.39500000000000002</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="12">
         <v>0.38</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="12">
         <v>0.39</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="12">
         <v>0.39</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="12">
         <v>0.38</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="12">
         <v>0.39</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="12">
         <v>0.39500000000000002</v>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="12">
         <v>0.38</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="12">
         <v>0.39</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="11">
+      <c r="A12" s="7">
         <v>46113</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="7">
         <v>46113</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="12">
         <v>0.37</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="12">
         <v>0.35</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="12">
         <v>0.36</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="12">
         <v>0.37</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="12">
         <v>0.35</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="12">
         <v>0.36</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="12">
         <v>0.37</v>
       </c>
-      <c r="L12" s="16">
+      <c r="L12" s="12">
         <v>0.35</v>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="12">
         <v>0.36</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="11">
+      <c r="A13" s="7">
         <v>46120</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="7">
         <v>46120</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="12">
         <v>0.36</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="12">
         <v>0.34</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="12">
         <v>0.35499999999999998</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="12">
         <v>0.36</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="12">
         <v>0.34</v>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="12">
         <v>0.35499999999999998</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="12">
         <v>0.36</v>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="12">
         <v>0.35</v>
       </c>
-      <c r="M13" s="16">
+      <c r="M13" s="12">
         <v>0.36</v>
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="11">
+      <c r="A14" s="7">
         <v>46127</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="7">
         <v>46127</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="12">
         <v>0.34</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="12">
         <v>0.33</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="12">
         <v>0.34</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="12">
         <v>0.34</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="12">
         <v>0.33</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="12">
         <v>0.34</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="12">
         <v>0.34</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="12">
         <v>0.33</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="12">
         <v>0.34</v>
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="11">
+      <c r="A15" s="7">
         <v>46134</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="7">
         <v>46134</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="12">
         <v>0.34</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="12">
         <v>0.33</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="12">
         <v>0.34</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="12">
         <v>0.33</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="12">
         <v>0.34</v>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="12">
         <v>0.33</v>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="12">
         <v>0.33500000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="11">
+      <c r="A16" s="7">
         <v>46141</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="7">
         <v>46141</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="12">
         <v>0.33</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="12">
         <v>0.33</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="12">
         <v>0.33</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="12">
         <v>0.33</v>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="12">
         <v>0.33</v>
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="11">
+      <c r="A17" s="7">
         <v>46155</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="7">
         <v>46155</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="12">
         <v>0.33</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="12">
         <v>0.33</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="12">
         <v>0.33</v>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="12">
         <v>0.33</v>
       </c>
-      <c r="M17" s="16">
+      <c r="M17" s="12">
         <v>0.33</v>
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="11">
+      <c r="A18" s="7">
         <v>46164</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="7">
         <v>46164</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="12">
         <v>0.33</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="12">
         <v>0.33</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="12">
         <v>0.33</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="12">
         <v>0.33</v>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="12">
         <v>0.33</v>
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="11">
+      <c r="A19" s="7">
         <v>46169</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="7">
         <v>46169</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="12">
         <v>0.33</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="12">
         <v>0.33</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="12">
         <v>0.33</v>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="12">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="12">
         <v>0.33</v>
       </c>
-      <c r="M19" s="16">
+      <c r="M19" s="12">
         <v>0.33</v>
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="11">
+      <c r="A20" s="7">
         <v>46176</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="7">
         <v>46176</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="12">
         <v>0.33</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="12">
         <v>0.32500000000000001</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="12">
         <v>0.33</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="12">
         <v>0.33</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="12">
         <v>0.32500000000000001</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="12">
         <v>0.33</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="12">
         <v>0.33</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="12">
         <v>0.32500000000000001</v>
       </c>
-      <c r="M20" s="16">
+      <c r="M20" s="12">
         <v>0.33</v>
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="11">
+      <c r="A21" s="7">
         <v>46183</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="7">
         <v>46183</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="12">
         <v>0.31</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="12">
         <v>0.3</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="12">
         <v>0.30499999999999999</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="12">
         <v>0.32500000000000001</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="12">
         <v>0.315</v>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="12">
         <v>0.32</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="12">
         <v>0.32</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="12">
         <v>0.31</v>
       </c>
-      <c r="M21" s="16">
+      <c r="M21" s="12">
         <v>0.315</v>
       </c>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="11">
+      <c r="A22" s="7">
         <v>46190</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="7">
         <v>46190</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="12">
         <v>0.29499999999999998</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="12">
         <v>0.28999999999999998</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="12">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="12">
         <v>0.31</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="12">
         <v>0.3</v>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="12">
         <v>0.30499999999999999</v>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="12">
         <v>0.3</v>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="12">
         <v>0.29499999999999998</v>
       </c>
-      <c r="M22" s="16">
+      <c r="M22" s="12">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="7">
+        <v>46197</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46197</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="12">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="F23" s="12">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H23" s="12">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="I23" s="12">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="J23" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="K23" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="L23" s="12">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M23" s="12">
+        <v>0.29499999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -10264,749 +10476,780 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:U23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="16"/>
-    <col min="22" max="16384" width="9" style="10"/>
+    <col min="1" max="1" width="10.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="8" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:21" s="5" customFormat="1">
+      <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="9" t="s">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="11">
+      <c r="A3" s="7">
         <v>46043</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="7">
         <v>46043</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="6">
         <v>0.82</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="6">
         <v>0.78</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="6">
         <v>0.79</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="6">
         <v>0.75</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="6">
         <v>0.71</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="6">
         <v>0.72</v>
       </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="11">
+      <c r="A4" s="7">
         <v>46050</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="7">
         <v>46050</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="6">
         <v>0.85</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="6">
         <v>0.78</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="6">
         <v>0.79</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="6">
         <v>0.82</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="6">
         <v>0.7</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="6">
         <v>0.76</v>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="11">
+      <c r="A5" s="7">
         <v>46057</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="7">
         <v>46057</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="12">
         <v>0.85</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="12">
         <v>0.78</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="12">
         <v>0.79</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="12">
         <v>0.82</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="12">
         <v>0.7</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="11">
+      <c r="A6" s="7">
         <v>46064</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="7">
         <v>46064</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="12">
         <v>0.85</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="12">
         <v>0.78</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="12">
         <v>0.79</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="12">
         <v>0.82</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="12">
         <v>0.7</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="11">
+      <c r="A7" s="7">
         <v>46078</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="7">
         <v>46078</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="12">
         <v>0.85</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="12">
         <v>0.78</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="12">
         <v>0.79</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="12">
         <v>0.82</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="12">
         <v>0.7</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="11">
+      <c r="A8" s="7">
         <v>46085</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="7">
         <v>46085</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="12">
         <v>0.85</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="12">
         <v>0.78</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="12">
         <v>0.79</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="12">
         <v>0.82</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="12">
         <v>0.7</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="11">
+      <c r="A9" s="7">
         <v>46092</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="7">
         <v>46092</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="12">
         <v>0.85</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="12">
         <v>0.78</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="12">
         <v>0.79</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="12">
         <v>0.82</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="12">
         <v>0.7</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="11">
+      <c r="A10" s="7">
         <v>46099</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="7">
         <v>46099</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="12">
         <v>0.85</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="12">
         <v>0.78</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="12">
         <v>0.79</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="12">
         <v>0.82</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="12">
         <v>0.7</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="11">
+      <c r="A11" s="7">
         <v>46106</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="7">
         <v>46106</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="12">
         <v>0.85</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="12">
         <v>0.78</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="12">
         <v>0.79</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="12">
         <v>0.82</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="12">
         <v>0.7</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="11">
+      <c r="A12" s="7">
         <v>46113</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="7">
         <v>46113</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="12">
         <v>0.85</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="12">
         <v>0.78</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="12">
         <v>0.79</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="12">
         <v>0.82</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="12">
         <v>0.7</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="11">
+      <c r="A13" s="7">
         <v>46120</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="7">
         <v>46120</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="12">
         <v>0.85</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="12">
         <v>0.78</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="12">
         <v>0.79</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="12">
         <v>0.82</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="12">
         <v>0.7</v>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="11">
+      <c r="A14" s="7">
         <v>46127</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="7">
         <v>46127</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="12">
         <v>0.85</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="12">
         <v>0.78</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="12">
         <v>0.79</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="12">
         <v>0.82</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="12">
         <v>0.7</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="11">
+      <c r="A15" s="7">
         <v>46134</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="7">
         <v>46134</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="12">
         <v>0.85</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="12">
         <v>0.78</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="12">
         <v>0.79</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="12">
         <v>0.82</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="12">
         <v>0.7</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="11">
+      <c r="A16" s="7">
         <v>46141</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="7">
         <v>46141</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="12">
         <v>0.8</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="12">
         <v>0.75</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="12">
         <v>0.78</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="12">
         <v>0.8</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="12">
         <v>0.75</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="11">
+      <c r="A17" s="7">
         <v>46155</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="7">
         <v>46155</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="12">
         <v>0.8</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="12">
         <v>0.75</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="12">
         <v>0.78</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="12">
         <v>0.8</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="12">
         <v>0.75</v>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="11">
+      <c r="A18" s="7">
         <v>46164</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="7">
         <v>46164</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="12">
         <v>0.8</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="12">
         <v>0.75</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="12">
         <v>0.78</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="12">
         <v>0.8</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="12">
         <v>0.75</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="11">
+      <c r="A19" s="7">
         <v>46169</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="7">
         <v>46169</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="12">
         <v>0.8</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="12">
         <v>0.75</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="12">
         <v>0.78</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="12">
         <v>0.8</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="12">
         <v>0.75</v>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="11">
+      <c r="A20" s="7">
         <v>46176</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="7">
         <v>46176</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="12">
         <v>0.78</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="12">
         <v>0.72</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="12">
         <v>0.75</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="12">
         <v>0.8</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="12">
         <v>0.75</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="11">
+      <c r="A21" s="7">
         <v>46183</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="7">
         <v>46183</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="12">
         <v>0.75</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="12">
         <v>0.72</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="12">
         <v>0.74</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="12">
         <v>0.8</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="12">
         <v>0.75</v>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="12">
         <v>0.76</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="11">
+      <c r="A22" s="7">
         <v>46190</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="7">
         <v>46190</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="12">
         <v>0.75</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="12">
         <v>0.7</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="12">
         <v>0.74</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="12">
         <v>0.8</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="12">
         <v>0.75</v>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="12">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="7">
+        <v>46197</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46197</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="12">
+        <v>0.74</v>
+      </c>
+      <c r="F23" s="12">
+        <v>0.71</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0.73</v>
+      </c>
+      <c r="H23" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="I23" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="J23" s="12">
         <v>0.76</v>
       </c>
     </row>
@@ -11024,937 +11267,977 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:U23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="15" customWidth="1"/>
-    <col min="6" max="13" width="9" style="15"/>
-    <col min="14" max="21" width="9" style="16"/>
-    <col min="22" max="16384" width="9" style="10"/>
+    <col min="1" max="1" width="10.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="11" customWidth="1"/>
+    <col min="6" max="13" width="9" style="11"/>
+    <col min="14" max="21" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="8" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:21" s="5" customFormat="1">
+      <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="7" t="s">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="11">
+      <c r="A3" s="7">
         <v>46043</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="7">
         <v>46043</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="4">
         <v>12</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="4">
         <v>11</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="4">
         <v>11.5</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="4">
         <v>19</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="4">
         <v>18</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="4">
         <v>18.5</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="4">
         <v>10</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="4">
         <v>9</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="4">
         <v>9.5</v>
       </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="11">
+      <c r="A4" s="7">
         <v>46050</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="7">
         <v>46050</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="4">
         <v>12</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="4">
         <v>11</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="4">
         <v>11.5</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="4">
         <v>19</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="4">
         <v>18</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="4">
         <v>18.5</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="4">
         <v>10</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="4">
         <v>9</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="4">
         <v>9.5</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="11">
+      <c r="A5" s="7">
         <v>46057</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="7">
         <v>46057</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="11">
         <v>12</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="11">
         <v>11</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="11">
         <v>11.5</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="11">
         <v>19</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="11">
         <v>18</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="11">
         <v>18.5</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="11">
         <v>10</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="11">
         <v>9</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="11">
         <v>9.5</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="11">
+      <c r="A6" s="7">
         <v>46064</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="7">
         <v>46064</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="11">
         <v>12</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="11">
         <v>11</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="11">
         <v>11.5</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="11">
         <v>19</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="11">
         <v>18</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="11">
         <v>18.5</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="11">
         <v>10</v>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="11">
         <v>9</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6" s="11">
         <v>9.5</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="11">
+      <c r="A7" s="7">
         <v>46078</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="7">
         <v>46078</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="11">
         <v>12</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="11">
         <v>11</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="11">
         <v>11.5</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="11">
         <v>19</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="11">
         <v>18</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="11">
         <v>18.5</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="11">
         <v>10</v>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="11">
         <v>9</v>
       </c>
-      <c r="M7" s="15">
+      <c r="M7" s="11">
         <v>9.5</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="11">
+      <c r="A8" s="7">
         <v>46085</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="7">
         <v>46085</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="11">
         <v>12</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="11">
         <v>11</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="11">
         <v>11.5</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="11">
         <v>19</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="11">
         <v>18</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="11">
         <v>18.5</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="11">
         <v>10</v>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="11">
         <v>9</v>
       </c>
-      <c r="M8" s="15">
+      <c r="M8" s="11">
         <v>9.5</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="11">
+      <c r="A9" s="7">
         <v>46092</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="7">
         <v>46092</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="11">
         <v>12</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="11">
         <v>11</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="11">
         <v>11.5</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="11">
         <v>19</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="11">
         <v>18</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="11">
         <v>18.5</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="11">
         <v>10</v>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="11">
         <v>9</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9" s="11">
         <v>9.5</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="11">
+      <c r="A10" s="7">
         <v>46099</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="7">
         <v>46099</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="11">
         <v>12</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="11">
         <v>11</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="11">
         <v>11.5</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="11">
         <v>19</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="11">
         <v>18</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="11">
         <v>18.5</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="11">
         <v>10</v>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="11">
         <v>9</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10" s="11">
         <v>9.5</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="11">
+      <c r="A11" s="7">
         <v>46106</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="7">
         <v>46106</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="11">
         <v>12</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="11">
         <v>11</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="11">
         <v>11.5</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="11">
         <v>19</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="11">
         <v>18</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J11" s="11">
         <v>18.5</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="11">
         <v>10</v>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="11">
         <v>9</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11" s="11">
         <v>9.5</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="11">
+      <c r="A12" s="7">
         <v>46113</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="7">
         <v>46113</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="11">
         <v>12</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="11">
         <v>11</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="11">
         <v>11.5</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="11">
         <v>19</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="11">
         <v>18</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="11">
         <v>18.5</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="11">
         <v>10</v>
       </c>
-      <c r="L12" s="15">
+      <c r="L12" s="11">
         <v>9</v>
       </c>
-      <c r="M12" s="15">
+      <c r="M12" s="11">
         <v>9.5</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="11">
+      <c r="A13" s="7">
         <v>46120</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="7">
         <v>46120</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="11">
         <v>11.5</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="11">
         <v>10.5</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="11">
         <v>11</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="11">
         <v>18.5</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="11">
         <v>17.5</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="11">
         <v>18</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="11">
         <v>9.5</v>
       </c>
-      <c r="L13" s="15">
+      <c r="L13" s="11">
         <v>8.5</v>
       </c>
-      <c r="M13" s="15">
+      <c r="M13" s="11">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="11">
+      <c r="A14" s="7">
         <v>46127</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="7">
         <v>46127</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="11">
         <v>11</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="11">
         <v>10</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="11">
         <v>10.5</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="11">
         <v>18.5</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="11">
         <v>17</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="11">
         <v>17.75</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="11">
         <v>9</v>
       </c>
-      <c r="L14" s="15">
+      <c r="L14" s="11">
         <v>8.5</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14" s="11">
         <v>8.75</v>
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="11">
+      <c r="A15" s="7">
         <v>46134</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="7">
         <v>46134</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="11">
         <v>11</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="11">
         <v>10</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="11">
         <v>10.5</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="11">
         <v>18.5</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="11">
         <v>17</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="11">
         <v>17.75</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="11">
         <v>9</v>
       </c>
-      <c r="L15" s="15">
+      <c r="L15" s="11">
         <v>8.5</v>
       </c>
-      <c r="M15" s="15">
+      <c r="M15" s="11">
         <v>8.75</v>
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="11">
+      <c r="A16" s="7">
         <v>46141</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="7">
         <v>46141</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="11">
         <v>11</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="11">
         <v>10</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="11">
         <v>10.5</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="11">
         <v>18.5</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="11">
         <v>17</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="11">
         <v>17.75</v>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="11">
         <v>9</v>
       </c>
-      <c r="L16" s="15">
+      <c r="L16" s="11">
         <v>8.5</v>
       </c>
-      <c r="M16" s="15">
+      <c r="M16" s="11">
         <v>8.75</v>
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="11">
+      <c r="A17" s="7">
         <v>46155</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="7">
         <v>46155</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="11">
         <v>11</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="11">
         <v>10</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="11">
         <v>10.5</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="11">
         <v>18.5</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="11">
         <v>17</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="11">
         <v>17.75</v>
       </c>
-      <c r="K17" s="15">
+      <c r="K17" s="11">
         <v>9</v>
       </c>
-      <c r="L17" s="15">
+      <c r="L17" s="11">
         <v>8.5</v>
       </c>
-      <c r="M17" s="15">
+      <c r="M17" s="11">
         <v>8.75</v>
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="11">
+      <c r="A18" s="7">
         <v>46164</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="7">
         <v>46164</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="11">
         <v>11</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="11">
         <v>10</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="11">
         <v>10.5</v>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="11">
         <v>18.5</v>
       </c>
-      <c r="I18" s="15">
+      <c r="I18" s="11">
         <v>17</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="11">
         <v>17.75</v>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="11">
         <v>9</v>
       </c>
-      <c r="L18" s="15">
+      <c r="L18" s="11">
         <v>8.5</v>
       </c>
-      <c r="M18" s="15">
+      <c r="M18" s="11">
         <v>8.75</v>
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="11">
+      <c r="A19" s="7">
         <v>46169</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="7">
         <v>46169</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="11">
         <v>11</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="11">
         <v>10</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="11">
         <v>10.5</v>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="11">
         <v>18.5</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I19" s="11">
         <v>17</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="11">
         <v>17.75</v>
       </c>
-      <c r="K19" s="15">
+      <c r="K19" s="11">
         <v>9</v>
       </c>
-      <c r="L19" s="15">
+      <c r="L19" s="11">
         <v>8.5</v>
       </c>
-      <c r="M19" s="15">
+      <c r="M19" s="11">
         <v>8.75</v>
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="11">
+      <c r="A20" s="7">
         <v>46176</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="7">
         <v>46176</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="11">
         <v>11</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="11">
         <v>10</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="11">
         <v>10.5</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="11">
         <v>18.5</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="11">
         <v>17</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="11">
         <v>17.75</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="11">
         <v>9</v>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="11">
         <v>8.5</v>
       </c>
-      <c r="M20" s="15">
+      <c r="M20" s="11">
         <v>8.75</v>
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="11">
+      <c r="A21" s="7">
         <v>46183</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="7">
         <v>46183</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="11">
         <v>10.5</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="11">
         <v>9.5</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="11">
         <v>10</v>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="11">
         <v>17</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="11">
         <v>16</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="11">
         <v>16.5</v>
       </c>
-      <c r="K21" s="15">
+      <c r="K21" s="11">
         <v>8.5</v>
       </c>
-      <c r="L21" s="15">
+      <c r="L21" s="11">
         <v>8</v>
       </c>
-      <c r="M21" s="15">
+      <c r="M21" s="11">
         <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="11">
+      <c r="A22" s="7">
         <v>46190</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="7">
         <v>46190</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="11">
         <v>10.5</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="11">
         <v>9.5</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="11">
         <v>10</v>
       </c>
-      <c r="H22" s="15">
+      <c r="H22" s="11">
         <v>17</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="11">
         <v>16</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="11">
         <v>16.5</v>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="11">
         <v>8.5</v>
       </c>
-      <c r="L22" s="15">
+      <c r="L22" s="11">
         <v>8</v>
       </c>
-      <c r="M22" s="15">
+      <c r="M22" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="7">
+        <v>46197</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46197</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="F23" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G23" s="11">
+        <v>10</v>
+      </c>
+      <c r="H23" s="11">
+        <v>17</v>
+      </c>
+      <c r="I23" s="11">
+        <v>16</v>
+      </c>
+      <c r="J23" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="K23" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="L23" s="11">
+        <v>8</v>
+      </c>
+      <c r="M23" s="11">
         <v>8</v>
       </c>
     </row>
@@ -11973,7 +12256,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9750F8-1F5B-4526-B393-530CBB79CB33}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11985,9 +12268,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
